--- a/Excel/3_1_Enteric_Feedlot_WIP_v02.prename.bak.xlsx
+++ b/Excel/3_1_Enteric_Feedlot_WIP_v02.prename.bak.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32501128-3D59-47C1-9E16-679DEB1B6662}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEA82253-4563-41A1-BA9B-C494BFBA0632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1590" yWindow="1560" windowWidth="31350" windowHeight="17460" activeTab="3" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="28800" windowHeight="15345" firstSheet="3" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -20,11 +20,14 @@
     <sheet name="Input - Feedlot" sheetId="70" r:id="rId5"/>
     <sheet name="3.1.1.1-2 Enteric Methane" sheetId="69" r:id="rId6"/>
     <sheet name="Constants - Feedlot" sheetId="79" r:id="rId7"/>
-    <sheet name="Constants - Common" sheetId="104" r:id="rId8"/>
+    <sheet name="Constants - Common" sheetId="105" r:id="rId8"/>
     <sheet name="Constants - Livestock" sheetId="43" r:id="rId9"/>
     <sheet name="Acknowledgements" sheetId="72" r:id="rId10"/>
     <sheet name="Tab template" sheetId="74" r:id="rId11"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId12"/>
+  </externalReferences>
   <definedNames>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e">_xlfn.LAMBDA(_xlpm.E_CH4,_xlpm.GWP_CH4, _xlpm.E_CH4 * _xlpm.GWP_CH4)</definedName>
     <definedName name="Common_Equations.Common_ConvertCH4ToCO2e_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"ECH4","Methane emissions (t CH4)";"GWPCH4","Global warming potential for methane (t CO2-e / t CH4)"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -181,6 +184,7 @@
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Variable">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Variation">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.";"Fixed typo - Changed 'Fry' to 'Dry'."}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData_DensityOfMethane_Data">'Constants - Common'!$D$175</definedName>
     <definedName name="CommonLivestock_InputFunctions.AverageLiveweightEndOfMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart,_xlpm.LiveweightAtStart,_xlpm.LiveweightGain, [0]!CommonLivestock_InputFunctions.LivestockMovement_ProportionalAverageLiveweightAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart) + [0]!CommonLivestock_InputFunctions.LivestockMovement_ProportionalAverageLiveweightRemainingAtEndOfMonth(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart, _xlpm.LiveweightAtStart, _xlpm.LiveweightGain))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_AverageLiveweightAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR([0]!CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass) / [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_GetMovementLiveweightGain" localSheetId="7">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.MovementDate, _xlfn.LET(_xlpm.ym, TEXT(_xlpm.MovementDate, "yyyymm"), IFERROR(INDEX(_xlfn._xlws.FILTER(#REF!, (TEXT(#REF!, "yyyymm") = _xlpm.ym) * (#REF! = _xlpm.LivestockClass)), 1), "")))</definedName>
@@ -236,6 +240,19 @@
     <definedName name="EntericMethane_Feedlot_Equations.VEERG_3_1_1_1__2_DailyEntericMethaneProduction_Variable">_xlfn.LAMBDA("M_j")</definedName>
     <definedName name="Fertiliser_Equations_InorganicCO2.VEERG_5_1_1_3__2_MassOfUreaInInorganicFertiliser_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(2, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"TM_jf","total mass of inorganic fertiliser type f applied to production system j : kg","Input";"FU_f","fraction of urea in fertiliser type f : kg urea/kg","Lookup"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="getOverlappingReportingCycles">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingStartMonth,_xlpm.ReportingStartDay, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, _xlpm.ReportingStartMonth, _xlpm.d, _xlpm.ReportingStartDay, _xlpm.A, _xlpm.S - 364, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (DATE(_xlpm.ya, _xlpm.m, _xlpm.d) &lt; _xlpm.A), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
+    <definedName name="Inoput_Cell_Livestock_antibiotics">#REF!</definedName>
+    <definedName name="Inoput_Cell_Livestockantibiotics">#REF!</definedName>
+    <definedName name="Input_Cell_CO2_for_carbonation">#REF!</definedName>
+    <definedName name="Input_Cell_CO2forcarbonation">#REF!</definedName>
+    <definedName name="Input_Cell_Livestock_antibiotics">#REF!</definedName>
+    <definedName name="Input_Cell_Livestock_tags">#REF!</definedName>
+    <definedName name="Input_Cell_LivestockAntibiotics">#REF!</definedName>
+    <definedName name="Input_Cell_Nylon_netting_for_horticulture">#REF!</definedName>
+    <definedName name="Input_Cell_Nylonnettingforhorticulture">#REF!</definedName>
+    <definedName name="Input_Cell_Pallets__Plastic">#REF!</definedName>
+    <definedName name="Input_Cell_Pallets__Wood">#REF!</definedName>
+    <definedName name="Input_Cell_Pallets_Plastic">#REF!</definedName>
+    <definedName name="Input_Cell_Pallets_Wood">#REF!</definedName>
     <definedName name="Input_Site_EndDate">'Input - Site'!$E$13</definedName>
     <definedName name="Input_Site_FarmName">'Input - Site'!$E$7</definedName>
     <definedName name="Input_Site_ReportingEntityName">'Input - Site'!$E$8</definedName>
@@ -5833,6 +5850,26 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Home"/>
+      <sheetName val="Constants - Common"/>
+      <sheetName val="Acknowledgements"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
 <rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
   <global>
@@ -5952,20 +5989,20 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{7160F4D5-69C3-498B-8768-94305C20B0A7}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{514F1257-9FFD-4A06-BEB3-327873B0D4AA}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
   <autoFilter ref="D6:F14" xr:uid="{E0906749-7FC7-47DE-82F6-F796C4463018}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{51475CB9-98D1-4367-81FE-766354D03859}" name="State/Territory">
+    <tableColumn id="1" xr3:uid="{C152B8B0-F310-4DBB-9B49-48BED2E695C2}" name="State/Territory">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{E5F4A4C1-F79D-42CE-8C7B-73B43952AF82}" name="Common Name">
+    <tableColumn id="2" xr3:uid="{45AC8637-58DF-4872-9C96-FEB7AD6BF947}" name="Common Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{1ED2BE90-6504-4529-96D4-F2168C2206DB}" name="Abbreviation">
+    <tableColumn id="3" xr3:uid="{1BD062A5-5588-423E-A20A-B7E81A43CFA5}" name="Abbreviation">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5974,12 +6011,12 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{AE790257-56EE-4D3A-9E9F-63BBBD489E9B}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{F8A6C99A-ADA3-41C7-96E2-554F9896A918}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
   <autoFilter ref="D20:D30" xr:uid="{5FA81339-C6C8-4D36-BEEA-6C4AEDD9E676}">
     <filterColumn colId="0" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{4834DA3C-E2C6-46A6-8B67-669901690AE1}" name="SA 4 Name">
+    <tableColumn id="1" xr3:uid="{190049B8-689A-4E22-A7E1-A08859A5EE69}" name="SA 4 Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5988,16 +6025,16 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{C748BD76-E957-4735-8DCC-4AA536F7251B}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{48DD1AAB-ABF0-45BE-B142-28C02310F073}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
   <autoFilter ref="D36:E43" xr:uid="{B8E87A66-3E41-4AD3-925D-01EE21B43D7A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{BC533CA1-A19D-4D88-851F-C6B55789EEF0}" name="Gas">
+    <tableColumn id="1" xr3:uid="{F643D369-C343-4011-BD35-602EFB10C326}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0744ED04-F9F9-4292-9C48-DCEC4CDB7B4B}" name="CO2-e factor">
+    <tableColumn id="2" xr3:uid="{41AE0BEA-86C3-4EBF-BC37-B324B34EECD4}" name="CO2-e factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6006,7 +6043,7 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{4DA84FD9-456A-4D76-8824-68BDCA1A0242}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{EC49DEDF-DE26-457F-854D-033636B33308}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
   <autoFilter ref="D47:H54" xr:uid="{C1F562BB-DAA6-45BB-951A-7BAFA5B64B45}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -6015,19 +6052,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{DE8A5F5D-380F-444B-895F-03A04F993303}" name="Gas">
+    <tableColumn id="1" xr3:uid="{84968D2C-9FC5-4EF7-8081-E6A28FBFD3F4}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{04DD10EA-0C74-4AE3-847F-091B6E17E288}" name="Conversion factor">
+    <tableColumn id="5" xr3:uid="{394453BB-BE98-4169-B1E0-C08CEC806CC6}" name="Conversion factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{B3B93DCD-8572-498D-8FD9-DE5161A70238}" name="Conversion factor 1">
+    <tableColumn id="2" xr3:uid="{E5AE10BF-894E-49B1-987D-E45F44EF3570}" name="Conversion factor 1">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{4AEFFF08-7C7F-45E3-BC84-7908AF11C801}" name="Conversion factor 2">
+    <tableColumn id="3" xr3:uid="{D2B72DC8-5AEE-46A3-A04F-CC97B488C0DD}" name="Conversion factor 2">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{C1AE1CC4-4B45-4D28-ACD1-DCB5A0BDE3F5}" name="Conversion factor combined">
+    <tableColumn id="4" xr3:uid="{C439E5B1-B5F9-42BE-87BC-8DC09F396A57}" name="Conversion factor combined">
       <calculatedColumnFormula>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6036,7 +6073,7 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{FE2FCFF0-2F5D-46AD-A562-2B5CA89C224F}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{FB26B50D-F016-46A8-8239-55ED56246A7D}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
   <autoFilter ref="D89:S97" xr:uid="{5A437AE9-7724-4CF2-ACCF-291078682FB9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -6056,52 +6093,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{BB64EF18-D941-4F52-A1B2-667BE97CB825}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{D60DA58E-B829-4C71-BDF8-1B2F6891D732}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{98934DD4-8710-4F12-95E3-FF8487499DD5}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{27E62255-EB41-42E6-AC44-A073C3FA0BB9}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{06CB93CF-EB6F-4172-85A6-ABDCD87EBE4A}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{3AA721EF-C414-4E64-B6AA-BA3C571C5992}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{9031FFF8-3C81-4F0A-BD57-02808D6AA1A2}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{AF6C16C4-8476-41BD-9A1E-505C48CC25EA}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{BEBBB14D-687E-40D7-8A5C-830F1BF21708}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{451408CF-48F8-4DE1-BB9A-4421C30E1403}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{59D992F0-26FC-4409-8EFD-219C6E95F62E}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{1623A147-4E8D-492F-89A6-638AED7900C5}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{9E1C5BA7-00D4-456C-BD35-A1A477A849E3}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{385D458A-83BF-4728-A479-BF84369BF1DC}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{B7E08E46-7D40-4A1B-85A5-2CBC68950E27}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{D876EAC2-AF08-49FE-9B6C-CDE7989EFA83}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{8DB33ADB-7FE8-4683-A42A-7B517C31FB73}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{B938A9A8-45AE-4A68-BCA7-9A745D70FB53}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{66872F0F-8733-4F0D-BAA4-7FB3E232EC5B}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{653F34A5-F52E-4677-8746-13A54EBF92E6}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{5BE2D3A3-9488-4CDA-A5C9-C914DE17BBDA}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{70E838A3-A75C-4F3F-81E5-6266275E71DD}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{87A2B35F-81EF-49FE-8E1C-DF65C2C68825}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{978E751B-0D52-42F9-AC95-5763E6EBF7B2}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{511CC549-5A99-4B0F-A28E-3A5AB574B811}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{9FE8CF28-4C0B-478C-A272-F255754E1CFE}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{9C4D55D3-27D4-4F56-AA8B-6A3586706EBF}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{A0FEAB60-34BD-4B40-9475-AC3E39E73FB0}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{96690360-D247-477E-86B7-F95A760E53DE}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{131ECD21-599C-4EEF-A295-27CCF4A40B4C}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{ADA6D733-164A-4027-9A96-8515CB5C69FD}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{500410B2-FE3C-4B9A-9AD8-967C18CBE996}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6110,16 +6147,16 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{84F274C9-B9BB-4501-85EC-CEB9C416829E}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{C6F83423-7DF4-41A5-8263-0C29E56778AC}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
   <autoFilter ref="D63:E77" xr:uid="{3597E019-B21E-4B76-BCC8-D02D497BCFA9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{AD84D891-CBE0-4BBE-A645-C24CA6B914EA}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{E7F87C1F-B811-4840-B256-69E32D64FFD6}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{BF4189CF-7E91-483C-B1DA-119B7CA28079}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{C5B74237-CC3F-4168-BA47-B1F2AAADA656}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6128,7 +6165,7 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{C652E3F2-AB22-4ACF-92AA-A6AEB37E80BD}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{E24D4C30-636C-4DBB-912E-DE120CF69005}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
   <autoFilter ref="D109:G112" xr:uid="{AB16FEAB-AB03-45E1-BBD4-66D29CD412DF}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -6136,16 +6173,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{C3C0E923-E589-4E34-8701-DB8EC6258A11}" name="Temperature Zone">
+    <tableColumn id="1" xr3:uid="{CA52AA3C-CA89-48F3-8EB2-2A603906105F}" name="Temperature Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{2B796427-73F3-481B-866C-FC3D56EAC122}" name="MAT">
+    <tableColumn id="2" xr3:uid="{A2B9AA01-382C-45E5-B91A-67D67D30AF46}" name="MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{72A35A9F-A175-428E-B2EB-AC78527D302C}" name="Min MAT">
+    <tableColumn id="3" xr3:uid="{3D48B33B-1F25-4CC3-8316-84653C521F29}" name="Min MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{CD803C3A-FF96-4FB2-82D8-DF68F7FD4FAF}" name="Max MAT">
+    <tableColumn id="4" xr3:uid="{69582A6D-1146-4472-A3C8-1A49081BE336}" name="Max MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6154,7 +6191,7 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{B1B19C0A-7DDB-4C72-962E-11F810EE97D9}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{58D80980-06E4-45E6-981C-63DD58B175D8}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
   <autoFilter ref="D119:G121" xr:uid="{E08772F3-2E8C-40A8-B755-08A5BBDF4130}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -6162,16 +6199,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{169E5E8D-C34D-47F5-B252-308C64B2880E}" name="Rainfall Zone">
+    <tableColumn id="1" xr3:uid="{7615802A-6D72-425D-9CE4-BC7D542C56CE}" name="Rainfall Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{8CFE46F1-75D3-4205-9E55-D423C5463F3F}" name="Annual rainfall">
+    <tableColumn id="2" xr3:uid="{E1DB465C-E06F-4F9D-A754-867F715DBD4B}" name="Annual rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{4B1B458B-AD21-49F5-8369-2CD9ED4BD265}" name="Min rainfall">
+    <tableColumn id="3" xr3:uid="{224BFC11-2477-4B45-B173-2056A7B51041}" name="Min rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{AF4E98C3-D944-414B-AF4E-208AC435F00D}" name="Max rainfall">
+    <tableColumn id="4" xr3:uid="{D5E137AF-235A-4427-AC29-3E4A6DCF1833}" name="Max rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6180,16 +6217,16 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{AC9C6153-67ED-43A0-BB11-3152817F4A35}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{5AB30CCE-77D5-4B5B-904A-973B0D815BBC}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
   <autoFilter ref="D127:E129" xr:uid="{A159E140-02ED-4547-B6E1-6695D8B16A11}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{B82FB12E-F809-4A9A-B37A-85414450FA6F}" name="Leaching Zone">
+    <tableColumn id="1" xr3:uid="{3354C849-8607-43D4-8D24-6C56D83022FA}" name="Leaching Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0FD0F4F6-7D42-4B2D-8796-FBB825513B17}" name="Leaching criteria">
+    <tableColumn id="2" xr3:uid="{642C1800-5B0A-4D13-A1FB-D691CAD334A8}" name="Leaching criteria">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6198,16 +6235,16 @@
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{1164EC0D-8973-4934-B8F1-FE2B07D75D6D}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="26" xr:uid="{147FB9FC-F771-4373-8260-0098BD2B1066}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
   <autoFilter ref="D153:E158" xr:uid="{133D42B0-F6D2-470A-858A-37E6A7F5EC2B}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{FEDF6BC1-FBEA-43D1-BAB8-589DC6D872BB}" name="Data source">
+    <tableColumn id="1" xr3:uid="{FC4B030D-100E-48C6-8A19-C9FFD21AD30A}" name="Data source">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{79475CCF-6312-464A-BB69-601104A11DDF}" name="Data score">
+    <tableColumn id="2" xr3:uid="{ECE3A7B5-F639-4631-8963-D8108DE9E335}" name="Data score">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6230,16 +6267,16 @@
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{EAACEA5C-382D-4B14-A21A-584728A7A10A}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{1AB46D37-5755-4A18-97F3-E358B0EDC07C}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
   <autoFilter ref="D134:E136" xr:uid="{308E99BE-FE1F-47A4-B2CA-97217277C4E9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{1E665611-2A06-4990-943E-3A4799B10AB6}" name="Is in leaching zone">
+    <tableColumn id="1" xr3:uid="{591521E2-42B6-43AE-BAF7-25FB48F19A8C}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{134E4DE7-4018-49B4-A248-DB8DC2091153}" name="FracWET" dataDxfId="19">
+    <tableColumn id="2" xr3:uid="{C4E89032-2375-4FDA-A7F2-387312E8EDF8}" name="FracWET" dataDxfId="19">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6248,7 +6285,7 @@
 </file>
 
 <file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="34" xr:uid="{4954D004-F7FF-487B-8ECC-8B6762D91454}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{66045F48-BB0A-4C8D-8B03-B93E4D2C6C5B}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
   <autoFilter ref="D186:H199" xr:uid="{D41FBEA4-8379-4DF7-A068-BF94D364F1A2}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -6257,19 +6294,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{6A40F661-DD2F-48D3-BEE9-E870DCD60A1F}" name="Production system j">
+    <tableColumn id="1" xr3:uid="{B9D6B5A6-37F2-451B-BA7F-C3737937AC79}" name="Production system j">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{DA9A0C1F-9EF4-45CB-83CE-2B2305C02ED1}" name="EFN2O">
+    <tableColumn id="2" xr3:uid="{33A93AC0-8CAF-43CC-A789-48AA6D6A0D05}" name="EFN2O">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{962D76BC-C77F-4BA9-B913-0F026AA43412}" name="Production system only">
+    <tableColumn id="3" xr3:uid="{5F09F312-EFAC-4BC4-A525-1BB6F76F6E1B}" name="Production system only">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{A3125B9E-6342-4A8E-8C3E-42B994D345EF}" name="Irrigation method">
+    <tableColumn id="4" xr3:uid="{0120D817-F5E6-40C1-ACC7-AC52D299FB39}" name="Irrigation method">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{95E9A13E-A6A1-455A-A238-C6E400DACCB6}" name="Rainfall zone">
+    <tableColumn id="5" xr3:uid="{74739519-6B0E-4A93-8AEB-CFBC84040ADB}" name="Rainfall zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6278,16 +6315,16 @@
 </file>
 
 <file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="35" xr:uid="{BA81D7DF-D521-47CD-9997-D2FA82C20439}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{E2C83720-EAFA-43E0-AB96-07947352D813}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
   <autoFilter ref="D142:E147" xr:uid="{1F48CA34-50DE-46D5-B32A-BB3A1E818E37}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{73A046A8-F626-4FF3-907F-4B0DAD89B65D}" name="Irrigation type i">
+    <tableColumn id="1" xr3:uid="{ABE996D6-7FFF-4757-AF1E-8B8AE0A43A75}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{EC56680E-26F7-4CD4-9B4E-8D94050B8B3A}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{13C88F98-E76F-4886-AAD1-3AE6BFC4DCA1}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6296,16 +6333,16 @@
 </file>
 
 <file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="36" xr:uid="{6BF6CDDB-DBF7-4904-BC00-BEC1CE565B2A}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{82BDAA0A-5F7E-489B-BD52-916924A9CD66}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
   <autoFilter ref="D206:E208" xr:uid="{D5BE3F89-D70E-4C53-A71C-E756622DEF38}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{DBA7DA6D-4FD9-48B7-8692-976739B5EBFA}" name="Climate zone">
+    <tableColumn id="1" xr3:uid="{1EAB483F-42C3-4A45-BF25-F1A5679BA057}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{8856FD95-9BF9-4137-9F2E-6A19B9836C4C}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{701E9542-D730-4405-BD2C-46F9E7E9789A}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6314,16 +6351,16 @@
 </file>
 
 <file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="37" xr:uid="{2768C421-456F-43F8-B739-653A2BE4EBEA}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="38" xr:uid="{2C59676A-B785-468F-BA1C-C6C208F0199C}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
   <autoFilter ref="D212:E224" xr:uid="{97796C3A-D95E-4077-AA20-A8FE4145DAAD}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{1FF9A772-EFFC-444F-BBE8-44684CE6962C}" name="Month">
+    <tableColumn id="1" xr3:uid="{9125ECE9-3ADB-40B4-B531-F3DA2F54CFFB}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{421B5A67-A1A2-4019-8983-556D10F00BD3}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{582A778C-7F9B-4D94-A7EC-BC86E6FCADDC}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6332,7 +6369,7 @@
 </file>
 
 <file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="39" xr:uid="{A0E07D5C-E8D0-4C56-A75B-4F8F7065DEC4}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="40" xr:uid="{BD30E199-7266-4CB7-A4BD-DD3CC4DB967D}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
   <autoFilter ref="D231:S250" xr:uid="{1D72DD9B-C8FA-48F4-9A11-20231FF87B5A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -6352,52 +6389,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{56135E2F-47ED-4165-BCE8-E09A9339B6EA}" name="Temperature zone">
+    <tableColumn id="1" xr3:uid="{0B947232-2215-4E5C-8BE6-82FC5948E9FE}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{4A87C324-8830-481A-BA66-519246FF91B8}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{EEEBDDC2-30D5-4EFF-A915-8F1E0A7B846F}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{98192B9B-A9EF-4BCA-8213-AD89F4FB17D1}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{7217E564-89AC-487A-838A-7954E87A0B9F}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{5DF4811D-6FFB-47B7-9A7A-BD1A91562CF1}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{33AE8184-2EB4-48C5-B874-9E826E7D1E90}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{9C930055-7DE9-48EA-9192-907B77F27A47}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{313B6A18-1A3E-4A16-8CCE-B535E36BE6F1}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{E7D04A66-911D-48C0-B67E-E2E95C60F3DB}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{47FDE51F-4140-4DF6-A107-72D5712E9140}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{09CE292C-B840-4D27-8590-8257B11311C1}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{3573E83E-46D5-48B1-BAE0-ACECC1197B12}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{1227B547-816D-47AC-A539-76F90520D98E}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{FC56180E-2D5D-4EFD-95AC-7A3C060EB8C1}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{BB1F7993-5EA3-44BA-AD58-97AAE49863D8}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{A68CF33F-9F43-4652-8EF5-8A553CA12AF0}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{DB863BF6-1410-4A46-8164-4B2A89B2BDC4}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{5ABEE273-FA33-4A93-B1C9-3D6C1ACE4C1E}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{DED0BC85-C592-41E0-B3A6-CFF080241C64}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{9D69E8E9-80D9-4142-9C6B-E27193081B94}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{4306A651-7FD4-4E5E-9FDA-21CC5A7F4900}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{BDF6EE34-FC92-48F9-B9B3-4F8AF211AFD9}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{04EBB78D-AEC6-4FC6-9C0E-0A40C564C66F}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{57C14148-A453-4436-9B20-4962AB8B7F03}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{B1AEE62D-B3E4-4300-8533-926546EAB1D2}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{6A43489F-01AE-470A-9ED3-AF64D8A2D8BE}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{E101CAF7-41B1-4308-B1E9-17F4ED339B8B}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{2C346730-0AF9-4587-98A5-DE005A3BAC9E}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{FC26A283-2E03-4AEC-B940-7DE455FCC417}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{C703CDD4-666B-4FCD-A94C-EA29E4926EC9}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6406,16 +6443,16 @@
 </file>
 
 <file path=xl/tables/table26.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="42" xr:uid="{2CE6C831-099B-49FD-A2C5-4C34BCDB4A39}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="41" xr:uid="{D66CFAC6-FEFD-4960-B662-EE72C65B775E}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
   <autoFilter ref="D257:E259" xr:uid="{56E01C14-1BB8-4015-9158-4CEB4D3B605C}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{225AAD2A-CB71-4DC4-987D-F99C09AD1EEA}" name="Climate Zone">
+    <tableColumn id="1" xr3:uid="{353E5E2B-C0FA-405D-B4AF-63E47BDD32A7}" name="Climate Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{7A889B50-9EC8-44AA-9CB8-C6FD4BE457A4}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{DF6D7C5F-94B7-4DCF-BABE-EE8D966EF291}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -18458,7 +18495,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06D75BB2-1C48-48CB-B0A9-6744D232A85A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D996979-5D34-4A3F-9D02-E3A93F8DD388}">
   <dimension ref="A1:BY259"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -23122,19 +23159,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBcAG4ARgByAGEAYwBXAEUAVABNAE0AUwBpACAAPQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4AKABUAGEAYgBsAGUAIABBADUALgA1AC4AMQAwAC4AMgAgAGkAcwAgAHIAZQBmAGUAcgBlAG4AYwBlAGQAIABpAG4AIABOAEkAUgAgAGIAdQB0ACAAMQAgAGkAcwAgAHUAcwBlAGQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAxACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXABuAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTACAAPQAgADAALgAwADIAIAAoAEcAZwAgAE4ALwBHAGcAIABhAHAAcABsAGkAZQBkACkAIAAoAEMAUwAgAEUARgAsACAAcwBvAHUAcgBjAGUAIABJAFAAQwBDACAAKAAyADAAMQA5ACkAKQAgAFwAbgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAIAAwAC4AMAAwADUAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsACAAMAAuADAAMAA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAgADAALgAwADAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAgADAALgAwADAANAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABjAGEAbgBlAFwAIgAsACAAMAAuADAAMQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAMAAuADAAMAA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAMAAuADAAMAA2ADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXABuAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAAVABhAGIAbABlACAANQAuADEAMgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB5AG0AYgBvAGwAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgAbQA9ADEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADIAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwAgACgAbQA9ADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAG0APQAzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGEAXAAiACwAIABcACIAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBTAHUAbQBwACAAYQBuAGQAIABkAGkAcwBwAGUAcgBzAGEAbAAgAHMAeQBzAHQAZQBtACAAKABtAD0AMwBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGIAXAAiACwAIABcACIARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAEQAcgBhAGkAbgBzACAAdABvACAAcABhAGQAZABvAGMAawAgACgAbQA9ADMAYgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIANABcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIAAoAG0APQA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA1AFwAIgAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAIAAoAG0APQA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA2AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQAgACgAbQA9ADYAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADcAXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwAgACgAbQA9ADcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADgAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgAgACgAbQA9ADgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADkAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQAgACgAbQA9ADkAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMABcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwAgACgAbQA9ADEAMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnACAAKABtAD0AMQAxACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADEAYQBcACIALAAgAFwAIgBCAGUAbAB0ACAAbQBhAG4AdQByAGUAIAByAGUAbQBvAHYAYQBsAFwAIgAsACAAXAAiAEIAZQBsAHQAIABtAGEAbgB1AHIAZQAgAHIAZQBtAG8AdgBhAGwAIAAoAG0APQAxADEAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAGIAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABzAHQAbwByAGUAZAAgAGkAbgAgAGgAbwB1AHMAZQBcACIALAAgAFwAIgBNAGEAbgB1AHIAZQAgAHMAdABvAHIAZQBkACAAaQBuACAAaABvAHUAcwBlACAAKABtAD0AMQAxAGIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAKABtAD0AMQAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADMAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAG0APQAxADMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEANABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAIAAoAG0APQAxADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBlAGUAZgAgAGMAYQB0AHQAbABlACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQB0AHQAbABlACwAIABmAG8AcgAgAG0AYQBuAHUAZgBhAGMAdAB1AHIAaQBuAGcAIABiAGUAZQBmAFwAIgAsACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBhAHQAdABsAGUALAAgAGYAbwByACAAcAByAGkAbQBlACAAYgBlAGUAZgBcACIALAAgAFwAIgBOAFMAVwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQB0AHQAbABlACwAIAB3AGUAYQBuAGUAcgBzAFwAIgAsACAAXAAiAE4AVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFEATABEAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAVABBAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBWAEkAQwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFcAQQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBDAGgAaQBjAGsAZQBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEMAaABpAGMAawBlAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBoAGkAYwBrAGUAbgBzACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQwBoAGkAYwBrAGUAbgBzAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEMAaABpAGMAawBlAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQwBoAGkAYwBrAGUAbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBDAGgAaQBjAGsAZQBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABcACIALAAgAFwAIgBTAG8AdQByAGMAZQAgAHIAZQBnAGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBoAGkAYwBrAGUAbgBzAFwAIgAsACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEQAYQBpAHIAeQBjAGEAdAB0AGwAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIABwAHIAbwBkAHUAYwB0AHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXwBWAGEAaQByAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8ARABhAGkAcgB5AGMAYQB0AHQAbABlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATABpAGYAZQBjAHkAYwBsAGUAcwAuACAAKAAyADAAMgA2ACkALgAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABHAGEAcwAgAEUAbQBpAHMAcwBpAG8AbgAgAEkAbgB0AGUAbgBzAGkAdABpAGUAcwAgAGYAbwByACAATQBhAHQAZQByAGkAYQBsACAASQBuAHAAdQB0AHMAIAB0AG8AIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAQQBnAHIAaQBjAHUAbAB0AHUAcgBlACwAIABGAGkAcwBoAGUAcgBpAGUAcwAgAGEAbgBkACAARgBvAHIAZQBzAHQAcgB5AC4AIABWAGUAcgBzAGkAbwBuACAANAA4AC4AIABkAG8AaQAgADEAMAAuADUAMgA4ADEALwB6AGUAbgBvAGQAbwAuADEAOQA2ADUANgA1ADgAMABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEQAYQBpAHIAeQBjAGEAdAB0AGwAZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AFwAIgAsACAAXAAiAFMAbwB1AHIAYwBlACAAcgBlAGcAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAaQByAHkAIABjAG8AdwBzAFwAIgAsACAAXAAiAFYASQBDAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBQAGkAZwBzACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUABpAGcAcwBfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAaQBnAHMAXAAiACwAIABcACIAQQB1AHMAdAByAGEAbABpAGEAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUwBoAGUAZQBwAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBTAGgAZQBlAHAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMAaABlAGUAcAAgAHAAcgBvAGQAdQBjAHQAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFMAaABlAGUAcABfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBTAGgAZQBlAHAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFMAaABlAGUAcABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBMAGkAZgBlAGMAeQBjAGwAZQBzAC4AIAAoADIAMAAyADYAKQAuACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEcAYQBzACAARQBtAGkAcwBzAGkAbwBuACAASQBuAHQAZQBuAHMAaQB0AGkAZQBzACAAZgBvAHIAIABNAGEAdABlAHIAaQBhAGwAIABJAG4AcAB1AHQAcwAgAHQAbwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABBAGcAcgBpAGMAdQBsAHQAdQByAGUALAAgAEYAaQBzAGgAZQByAGkAZQBzACAAYQBuAGQAIABGAG8AcgBlAHMAdAByAHkALgAgAFYAZQByAHMAaQBvAG4AIAA0ADgALgAgAGQAbwBpACAAMQAwAC4ANQAyADgAMQAvAHoAZQBuAG8AZABvAC4AMQA5ADYANQA2ADUAOAAwAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUwBoAGUAZQBwAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAaABlAGUAcAAsACAAZgBvAHIAIABtAHUAdAB0AG8AbgBcACIALAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAaABlAGUAcAAsACAAZgBvAHIAIABwAHIAaQBtAGUAIABsAGEAbQBiAFwAIgAsACAAXAAiAE4AUwBXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAUQBMAEQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBTAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFYASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAVwBBAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFIATwBXACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACAALQAgADEAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAVABhAGIAbABlAEgAZQBhAGQAZQByAEMAZQBsAGwALABcAG4AIAAgAEMATwBMAFUATQBOACgAVABhAGIAbABlAEgAZQBhAGQAZQByAEMAZQBsAGwAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIABBAHIAcgBhAHkARABhAHQAYQAsACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALAAgAFsAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQBdACwAXABuACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAASQBOAEQARQBYACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFUATgBJAFEAVQBFACgAQQByAHIAYQB5AEQAYQB0AGEAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkALAAgADEALAAgAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALAAgAFwAIgBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABJAEYAKABJAFMATgBVAE0AQgBFAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACAAIAAgACAAKQAsACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQAsACAAMAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIAAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADEAKQAqACgATABvAG8AawB1AHAAQQByAHIAYQB5ADIAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgApACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAKQApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABDAGUAbABsACwAIABEAGUAbABpAG0AaQB0AGUAcgAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQBdACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyAF0ALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSAFgATQBMACgAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMAdABcAHUAMAAwADMAZQBcAHUAMAAwADMAYwBzAFwAdQAwADAAMwBlAFwAIgAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwBzAFwAdQAwADAAMwBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgACkAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMALwB0AFwAdQAwADAAMwBlAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AZQBsAGUAdgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZQBsAGUAdgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFAARQBUAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AbQBhAHAAXwBwAGUAdAApACwAXABuACAAIAAgACAAIAAgACAAIABUAEEASwBFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAMQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATQBpAG4AQQByAHIAYQB5ACwAIABNAGEAeABBAHIAcgBhAHkALAAgAEkAdABlAG0AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBpAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGEAeABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAIABTACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUAIABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAIAAvACoAaABlAGwAcABlAHIAOgAgAGUAbgBkACAAZABhAHQAZQAgAGYAbwByACAAYQAgAHIAZQBwAG8AcgB0AGkAbgBnACAAcABlAHIAaQBvAGQAIABzAHQAYQByAHQAaQBuAGcAIABhAHQAIABhACAAZwBpAHYAZQBuACAAZABhAHQAZQAqAC8AXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALAAgAC8AKgBvAG4AbAB5ACAAbgBlAGUAZAAgAHQAbwAgAGwAbwBvAGsAIABiAGEAYwBrACAAMwA2ADUAIABkAGEAeQBzACgAbQBhAHgAIABvAHYAZQByAGwAYQBwACAAdwBpAG4AZABvAHcAKQAqAC8AXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBhACAAZQBuAGQAcwAgAGIAZQBmAG8AcgBlACAAUwAsAGkAdAAgAGMAYQBuAFwAdQAwADAAMgA3AHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQBcAHUAMAAwADMAYwBTACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGIAIABzAHQAYQByAHQAcwAgAGEAZgB0AGUAcgAgAEUALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAHAAcgBlAHYAaQBvAHUAcwAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQBcAHUAMAAwADMAZQBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbgA9ADAALABcACIAXAAiACwASABTAFQAQQBDAEsAKABzAHQAYQByAHQAcwBUAGUAeAB0ACAAXAB1ADAAMAAyADYAIABcACIAIAB0AG8AIABcACIAIABcAHUAMAAwADIANgAgAGUAbgBkAHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAdABhAGcAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlAFwAbgA9AEwAQQBNAEIARABBACgARgB1AG4AYwB0AGkAbwBuACwAIABUAEUAWABUAEIARQBGAE8AUgBFACgARgBPAFIATQBVAEwAQQBUAEUAWABUACgARgB1AG4AYwB0AGkAbwBuACkALAAgAFwAIgAoAFwAIgApACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQAsAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAD0AXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAIAA9ACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkAPQBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQA9AEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQA9AFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAgACsAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQAXAB1ADAAMAAzAGUAMAAsACAAMQAsACAAMAApAFwAbgAgACAAIAAgACkAKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAB1ADAAMAAyADcAXAAiACAAXAB1ADAAMAAyADYAIABzAGgAIABcAHUAMAAwADIANgAgAFwAIgBcAHUAMAAwADIANwAhAFwAIgAgAFwAdQAwADAAMgA2ACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBEAGkAZgBmAGUAcgBlAG4AdABTAGgAZQBlAHQAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADEAXwAyAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsACAAMQAsACAAMgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADMAXwA0AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsACAAMwAsACAANAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEcAZQB0AE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABNAE0AUwAsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAXABuACAAIAAgACAAIAAgACAAIABNAEUARABJAEEATgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAaQB0AGwAZQBDAGUAbABsACwAIABTAG8AdQByAGMAZQBDAGUAbABsACwAXABuACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAEwARQBGAFQAKABTAG8AdQByAGMAZQBDAGUAbABsACwAIABGAEkATgBEACgAXAAiACwAXAAiACwAIABTAG8AdQByAGMAZQBDAGUAbABsACkAIAAtADEAKQAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFwAIgAsACAAXAAiAFwAIgApACAAXAB1ADAAMAAyADYAIABcACIAIABcACIAIABcAHUAMAAwADIANgAgAFQAaQB0AGwAZQBDAGUAbABsAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAbABvAHMAdAAgAGkAbgAgAHQAaABlACAAcAByAGkAbQBhAHIAeQAgAE0ATQBTAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAZQBlAGQAbABvAHQAIAAtACAARgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIABsAG8AcwB0ACAAZAB1AHIAaQBuAGcAIABzAHQAbwByAGEAZwBlACAAaQBuACAAdABoAGUAIABwAHIAaQBtAGEAcgB5ACAAcwB5AHMAdABlAG0AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAUwBMAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADUAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAHQAbwAgAGUAYQBjAGgAIAB0AGUAcgB0AGkAYQByAHkAIABzAHkAcwB0AGUAbQAgAGEAcwBzAHUAbQBlAGQAIAB0AGgAYQB0ACAAMgAgAHAAZQByACAAYwBlAG4AdAAgAGkAcwAgAHIAdQBuACAALQAgAG8AZgBmACAAZgByAG8AbQAgAHQAaABlACAAZgBlAGUAZAAgAHAAYQBkAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAHQAbwAgAGUAYQBjAGgAIAB0AGUAcgB0AGkAYQByAHkAIABzAHkAcwB0AGUAbQAgAGEAcwBzAHUAbQBlAGQAIAB0AGgAYQB0ACAAMgAgAHAAZQByACAAYwBlAG4AdAAgAGkAcwAgAHIAdQBuACAALQAgAG8AZgBmACAAZgByAG8AbQAgAHQAaABlACAAZgBlAGUAZAAgAHAAYQBkAC4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBNAFMAbQAxAFQAMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAyAC4AMwAgAEMATwBOAFMAVABBAE4AVABTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADAAMgApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXABuAEEAcwBoACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAG0AYQBuAHUAcgBlAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHMAaAAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABtAGEAbgB1AHIAZQAuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgAxADYAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAFwAbgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbAAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAcABvAHQAZQBuAHQAaQBhAGwALgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBCADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAG0AMwAgAEMASAA0ACAALwAgAGsAZwAgAFYAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgAxADkAKQA7AFwAbgBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AUwB0AGEAZwBlADEATQBNAFMATwBwAHQAaQBvAG4AcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADEALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAbABvAHQAIAAoAGYAZQBlAGQAIABwAGEAZAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBTAHQAYQBnAGUAMgBNAE0AUwBPAHAAdABpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAMQAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAATQBNAFMAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFMAdABhAGcAZQAzAE0ATQBTAE8AcAB0AGkAbwBuAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAxACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwBlAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwBcACIAOwAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAHgAcABvAHIAdAAgAG0AaQBkACAAZgBlAGQAXAAiADsAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQB4AHAAbwByAHQAIABsAG8AbgBnACAAZgBlAGQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMQAuADEAOgAgAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAARAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgACgAZABhAHkAcwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEQAdQByAGEAdABpAG8AbgAgAG8AZgAgAHMAdABhAHkAIAAoAGQAYQB5AHMAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAxAC4AMQA6ACAAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABEAHUAcgBhAHQAaQBvAG4AIABvAGYAIABzAHQAYQB5ACAAKABkAGEAeQBzACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAZQBkAGwAbwB0ACAAdAB5AHAAZQBcACIALAAgAFwAIgBMAGUAbgBnAHQAaAAgAG8AZgAgAFMAdABhAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwBcACIALAAgAFwAIgAxAC0AOAAwACAAZABhAHkAcwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBpAGQALQBmAGUAZABcACIALAAgAFwAIgA4ADEALQAyADAAMAAgAGQAYQB5AHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwBuAGcALQBmAGUAZABcACIALAAgAFwAIgAyADAAMQArACAAZABhAHkAcwBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAG4AaQBtAGEAbABDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBcAG4AVABhAGIAbABlACAAQQAuADEALgAxAC4AMgA6ACAAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABBAG4AaQBtAGEAbAAgAGMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBuAGkAbQBhAGwAQwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAAQQBuAGkAbQBhAGwAIABjAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAG4AaQBtAGEAbABDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAbgBpAG0AYQBsAEMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMQAuADIAOgAgAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAAQQBuAGkAbQBhAGwAIABjAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAG4AaQBtAGEAbABDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AdgBlAGQAIABmAGUAZQBkAGwAbwB0ACAAdAB5AHAAZQBzACAAdABvACAAYQAgAHMAZQBwAGEAcgBhAHQAZQAgAGMAbwBsAHUAbQBuACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAGEAbQBlAGQAIABcAHUAMAAwADIANwBjAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAC0AIABvAHIAaQBnAGkAbgBhAGwAIABoAGEAcwAgAGgAZQBhAGQAZQByACAAXAB1ADAAMAAyADcAVQBuAGkAdABcAHUAMAAwADIANwAgAHcAaABpAGMAaAAgAGMAbwB2AGUAcgBzACAAdAB3AG8AIABjAG8AbAB1AG0AbgBzACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAbgBpAG0AYQBsAEMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMAAsACAANwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBlAGUAZABsAG8AdAAgAHQAeQBwAGUAXAAiACwAIABcACIAQwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAFwAIgAsACAAXAAiAFUAbgBpAHQAXAAiACwAIABcACIAMgAwADAANQAtADIAMAAwADkAXAAiACwAIABcACIAMgAwADEAMAAtADIAMAAxADQAXAAiACwAIABcACIAMgAwADEANQAtADIAMAAxADkAXAAiACwAIABcACIAMgAwADIAMAAtADIAMAAyADMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwBcACIALAAgAFwAIgBEAGEAeQBzACAAbwBuACAAZgBlAGUAZABcACIALAAgAFwAIgBkAGEAeQBzAFwAIgAsACAANwAwACwAIAA3ADAALAAgADcAMAAsACAANwA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwBcACIALAAgAFwAIgBGAGUAZQBkACAAaQBuAHQAYQBrAGUAXAAiACwAIABcACIAawBnACAARABNAC8AZABhAHkAXAAiACwAIAAxADAALgAwACwAIAAxADAALgAwACwAIAAxADAALgA0ACwAIAAxADAALgA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwBcACIALAAgAFwAIgBOACAAcgBlAHQAZQBuAHQAaQBvAG4AXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0ACAAbwBmACAAaQBuAHQAYQBrAGUAXAAiACwAIAAyADEALgAxACwAIAAyADAALgA0ACwAIAAyADAALgA0ACwAIAAyADAALgA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBkAC0AZgBlAGQAXAAiACwAIABcACIARABhAHkAcwAgAG8AbgAgAGYAZQBlAGQAXAAiACwAIABcACIAZABhAHkAcwBcACIALAAgADEAMQA1ACwAIAAxADEANQAsACAAMQAyADAALAAgADEANQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBkAC0AZgBlAGQAXAAiACwAIABcACIARgBlAGUAZAAgAGkAbgB0AGEAawBlAFwAIgAsACAAXAAiAGsAZwAgAEQATQAvAGQAYQB5AFwAIgAsACAAMQAxAC4AMgAsACAAMQAwAC4AOAAsACAAMQAwAC4AOAAsACAAMQAwAC4AOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGkAZAAtAGYAZQBkAFwAIgAsACAAXAAiAE4AIAByAGUAdABlAG4AdABpAG8AbgBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAIABvAGYAIABpAG4AdABhAGsAZQBcACIALAAgADEAMgAuADUALAAgADEAMgAuADcALAAgADEAMgAuADcALAAgADEAMgAuADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAG4AZwAtAGYAZQBkAFwAIgAsACAAXAAiAEQAYQB5AHMAIABvAG4AIABmAGUAZQBkAFwAIgAsACAAXAAiAGQAYQB5AHMAXAAiACwAIAAyADUAMAAsACAAMgA1ADAALAAgADIANQAwACwAIAAyADUAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AbgBnAC0AZgBlAGQAXAAiACwAIABcACIARgBlAGUAZAAgAGkAbgB0AGEAawBlAFwAIgAsACAAXAAiAGsAZwAgAEQATQAvAGQAYQB5AFwAIgAsACAAOQAuADAALAAgADgALgA1ACwAIAA4AC4AMgAsACAAOAAuADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAG4AZwAtAGYAZQBkAFwAIgAsACAAXAAiAE4AIAByAGUAdABlAG4AdABpAG8AbgBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAIABvAGYAIABpAG4AdABhAGsAZQBcACIALAAgADYALgA2ACwAIAA3AC4AMAAsACAANwAuADAALAAgADcALgAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBcAG4AVABhAGIAbABlACAAQQAuADEALgAxAC4AMwA6ACAAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABEAGkAZQB0ACAAcAByAG8AcABlAHIAdABpAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABEAGkAZQB0ACAAcAByAG8AcABlAHIAdABpAGUAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAGkAZQB0AFAAcgBvAHAAZQByAHQAaQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAGkAZQB0AFAAcgBvAHAAZQByAHQAaQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAxAC4AMwA6ACAAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABEAGkAZQB0ACAAcAByAG8AcABlAHIAdABpAGUAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAGkAZQB0AFAAcgBvAHAAZQByAHQAaQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAQwBvAG4AdgBlAHIAdABlAGQAIAB0AG8AIABmAHIAYQBjAHQAaQBvAG4AIABjAG8AbAB1AG0AbgAgAGEAbgBkACAAYwBvAG4AdgBlAHIAdABlAGQAIABOAEQARgAgAGEAbgBkACAARQB0AGgAZQByACAAZQB4AHQAcgBhAGMAdAAgAHYAYQBsAHUAZQBzACAAdABvACAAZgByAGEAYwB0AGkAbwBuAHMALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAHYAZQBkACAAZgBlAGUAZABsAG8AdAAgAHQAeQBwAGUAcwAgAHQAbwAgAGEAIABzAGUAcABhAHIAYQB0AGUAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARABpAGUAdABQAHIAbwBwAGUAcgB0AGkAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAOAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBlAGUAZABsAG8AdAAgAHQAeQBwAGUAXAAiACwAIABcACIATgB1AHQAcgBpAGUAbgB0ACAAYQBuAGEAbAB5AHMAaQBzAFwAIgAsACAAXAAiAFUAbgBpAHQAXAAiACwAIABcACIAMgAwADAANQAtADIAMAAwADkAXAAiACwAIABcACIAMgAwADEAMAAtADIAMAAxADQAXAAiACwAIABcACIAMgAwADEANQAtADIAMAAxADkAXAAiACwAIABcACIAMgAwADIAMAAtADIAMAAyADMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAdABlAGQAIAB0AG8AIABmAHIAYQBjAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwBcACIALAAgAFwAIgBEAHIAeQAgAG0AYQB0AHQAZQByACAAZABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIAAwAC4AOAAxACwAIAAwAC4AOAAxACwAIAAwAC4AOAAxACwAIAAwAC4AOAAxACwAIAAwAC4AOAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwBcACIALAAgAFwAIgBDAHIAdQBkAGUAIABwAHIAbwB0AGUAaQBuAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgADAALgAxADQALAAgADAALgAxADQALAAgADAALgAxADQALAAgADAALgAxADQALAAgADAALgAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjAFwAIgAsACAAXAAiAE4ARABGAFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdABcACIALAAgADIAMwAuADAALAAgADIAMgAuADAALAAgADIAMgAuADAALAAgADIAMgAuADAALAAgADAALgAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjAFwAIgAsACAAXAAiAEUAdABoAGUAcgAgAEUAeAB0AHIAYQBjAHQAXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0AFwAIgAsACAANAAuADUALAAgADQALgA1ACwAIAA0AC4AOAAsACAANAAuADgALAAgADAALgAwADQAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGkAZAAtAGYAZQBkAFwAIgAsACAAXAAiAEQAcgB5ACAAbQBhAHQAdABlAHIAIABkAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5AFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgADAALgA4ADEALAAgADAALgA4ADEALAAgADAALgA4ADEALAAgADAALgA4ADEALAAgADAALgA4ADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBpAGQALQBmAGUAZABcACIALAAgAFwAIgBDAHIAdQBkAGUAIABwAHIAbwB0AGUAaQBuAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgADAALgAxADMALAAgADAALgAxADIANQAsACAAMAAuADEAMgAsACAAMAAuADEAMgAsACAAMAAuADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGkAZAAtAGYAZQBkAFwAIgAsACAAXAAiAE4ARABGAFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdABcACIALAAgADIANAAuADAALAAgADIAMgAuADAALAAgADIAMgAuADAALAAgADIAMgAuADAALAAgADAALgAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBpAGQALQBmAGUAZABcACIALAAgAFwAIgBFAHQAaABlAHIAIABFAHgAdAByAGEAYwB0AFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdABcACIALAAgADUALgAwACwAIAA1AC4AMAAsACAANQAuADAALAAgADUALgAwACwAIAAwAC4AMAA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwBuAGcALQBGAGUAZABcACIALAAgAFwAIgBEAHIAeQAgAG0AYQB0AHQAZQByACAAZABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIAAwAC4AOAAxACwAIAAwAC4AOAAxACwAIAAwAC4AOAAxACwAIAAwAC4AOAAxACwAIAAwAC4AOAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwBuAGcALQBGAGUAZABcACIALAAgAFwAIgBDAHIAdQBkAGUAIABwAHIAbwB0AGUAaQBuAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgADAALgAxADMALAAgADAALgAxADIANQAsACAAMAAuADEAMgAsACAAMAAuADEAMgAsACAAMAAuADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AbgBnAC0ARgBlAGQAXAAiACwAIABcACIATgBEAEYAXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0AFwAIgAsACAAMgA0AC4AMAAsACAAMgA0AC4AMAAsACAAMgA0AC4AMAAsACAAMgA0AC4AMAAsACAAMAAuADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AbgBnAC0ARgBlAGQAXAAiACwAIABcACIARQB0AGgAZQByACAARQB4AHQAcgBhAGMAdABcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIAA1AC4AMAAsACAANQAuADAALAAgADUALgA1ACwAIAA1AC4ANQAsACAAMAAuADAANQA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAEMARgBcAG4AVABhAGIAbABlACAAQQAuADEALgAxAC4ANAA6ACAAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABNAEMARgBzACAAKABmAHIAYQBjAHQAaQBvAG4AKQAgACgATQBDAEYAaQBtAFQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AQwBGAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGUAZQBkAGwAbwB0ACAALQAgAE0AQwBGAHMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBDAEYAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAEMARgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADEALgA0ADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAE0AQwBGAHMAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AVAApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AQwBGAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAdQBwAGwAaQBjAGEAdABlAGQAIABOAFMAVwAgAHYAYQBsAHUAZQBzACAAZgBvAHIAIABBAEMAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAATgBUACAAYwBvAGwAdQBtAG4AIAB0AGgAYQB0ACAAZAB1AHAAbABpAGMAYQB0AGUAcwAgAFEATABEACAAdgBhAGwAdQBlAHMAIABhAHMAIABwAGUAcgAgAGEAZAB2AGkAYwBlACAAZgByAG8AbQAgAHMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHAAcgBvAHYAaQBkAGUAcgAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABUAEEAUwAgAGMAbwBsAHUAbQBuACAAdABoAGEAdAAgAGQAdQBwAGwAaQBjAGEAdABlAHMAIABWAEkAQwAgAHYAYQBsAHUAZQBzACAAYQBzACAAcABlAHIAIABhAGQAdgBpAGMAZQAgAGYAcgBvAG0AIABzAG8AdQByAGMAZQAgAGQAYQB0AGEAIABwAHIAbwB2AGkAZABlAHIALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAATQBNAFMAIABuAGEAbQBlAHMAIAB0AGgAYQB0ACAAbQBhAHQAYwBoACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBDAEYAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMQAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgAFQAXAAiACwAIABcACIATQBNAFMAIABtAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAXAAiAE4AVABcACIALAAgAFwAIgBTAEEAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIABcACIAVwBBAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAXAAiAE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAGkAbQBhAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGwAbwB0ACAAKABGAGUAZQBkAHAAYQBkACkAXAAiACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAzACwAIAAwAC4AMAAzACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIABcACIARAByAHkAbABvAHQAIAAoAGYAZQBlAGQAIABwAGEAZAApAFwAIgA7ACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBjAG8AbgBkAGEAcgB5AFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAIAAoAFMAdABvAGMAawBwAGkAbABlACkAXAAiACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIABcACIAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcACIAOwAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGUAYwBvAG4AZABhAHIAeQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABQAGEAcwBzAGkAdgBlACAAVwBpAG4AZAByAG8AdwApAFwAIgAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiADsAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAGMAbwBuAGQAYQByAHkAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AIAB0AG8AIABzAG8AaQBsAFwAIgAsACAAMAAsACAAMAAsACAAMAAsACAAMAAsACAAMAAsACAAMAAsACAAMAAsACAAMAAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgA7ACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQByAHQAaQBhAHIAeQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AIAAoAEUAZgBmAGwAdQBlAG4AdAAgAHAAbwBuAGQAKQBcACIALAAgADAALgA3ADUALAAgADAALgA3ADUALAAgADAALgA3ADcALAAgADAALgA3ADcALAAgADAALgA3ADUALAAgADAALgA3ADUALAAgADAALgA3ADcALAAgADAALgA3ADUALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADEALgA1ADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABFAEYAcwAgACgARQBGAG0AVAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAZQBlAGQAbABvAHQAIAAtACAATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAEUARgBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAxAC4ANQA6ACAAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAARQBGAHMAIAAoAEUARgBtAFQAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABcAHUAMAAwADIANwBOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABNAE0AUwAgAG4AYQBtAGUAcwAgAHQAaABhAHQAIABtAGEAdABjAGgAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgAFQAXAAiACwAIABcACIATQBNAFMAIABtAFwAIgAsACAAXAAiAEUARgBtAFQAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQBcACIALAAgAFwAIgBOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBpAG0AYQByAHkAXAAiACwAIABcACIARAByAHkAIABsAG8AdAAgACgARgBlAGUAZABwAGEAZAApAFwAIgAsACAAMAAuADAAMAA1ADQALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBjAG8AbgBkAGEAcgB5AFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAIAAoAFMAdABvAGMAawBwAGkAbABlACkAXAAiACwAIAAwAC4AMAAwADUALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGUAYwBvAG4AZABhAHIAeQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABQAGEAcwBzAGkAdgBlACAAVwBpAG4AZAByAG8AdwApAFwAIgAsACAAMAAuADAAMQAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBjAG8AbgBkAGEAcgB5AFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAQQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgADAALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAHIAdABpAGEAcgB5AFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgARQBmAGYAbAB1AGUAbgB0ACAAUABvAG4AZAApAFwAIgAsACAAMAAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARgByAGEAYwBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABcAG4AVABhAGIAbABlACAAQQAuADEALgAxAC4ANgA6ACAAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAYgB5ACAATQBNAFMAIAAoAEYAcgBhAGMARwBBAFMATQBtAFQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEYAcgBhAGMATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAZQBlAGQAbABvAHQAIAAtACAARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGIAeQAgAE0ATQBTACAAKABGAHIAYQBjAEcAQQBTAE0AbQBUACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARgByAGEAYwBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEYAcgBhAGMATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAxAC4ANgA6ACAAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAYgB5ACAATQBNAFMAIAAoAEYAcgBhAGMARwBBAFMATQBtAFQAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBGAHIAYQBjAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgBcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuACAAdwBpAHQAaAAgAE0ATQBTACAAbgBhAG0AZQBzACAAdABoAGEAdAAgAG0AYQB0AGMAaAAgAE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEYAcgBhAGMATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIABUAFwAIgAsACAAXAAiAE0ATQBTACAAbQBcACIALAAgAFwAIgBGAHIAYQBjAEcAQQBTAE0AbQBUACAAKABrAGcAIABOAEgAMwAtAE4AIAArACAATgBPAHgALQBOACkALwBrAGcAIABOAFwAIgAsACAAXAAiAE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAGkAbQBhAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGwAbwB0ACAAKABGAGUAZQBkAHAAYQBkACkAXAAiACwAIAAwAC4ANgAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAGMAbwBuAGQAYQByAHkAXAAiACwAIABcACIAUwBvAGwAaQBkACAAUwB0AG8AcgBhAGcAZQAgACgAUwB0AG8AYwBrAHAAaQBsAGUAKQBcACIALAAgADAALgAyADUALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGUAYwBvAG4AZABhAHIAeQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABQAGEAcwBzAGkAdgBlACAAVwBpAG4AZAByAG8AdwApAFwAIgAsACAAMAAuADQALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGUAYwBvAG4AZABhAHIAeQBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHQAbwAgAHMAbwBpAGwAXAAiACwAIAAwACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQByAHQAaQBhAHIAeQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AIAAoAEUAZgBmAGwAdQBlAG4AdAAgAHAAbwBuAGQAKQBcACIALAAgADAALgAzADUALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBGAGUAZQBkAGwAbwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADMALgAxADoAIABFAG4AdABlAHIAaQBjACAATQBlAHQAaABhAG4AZQAgAC0AIABGAGUAZQBkAGwAbwB0ACAAQgBlAGUAZgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMwAuADEALgAxAC4AMQAgAE0AZQB0AGgAbwBkACAAMQAgAC0AIABFAG4AdABlAHIAaQBjACAAQgBlAGUAZgAgAEYAZQBlAGQAbABvAHQAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAFwAbgBUAG8AdABhAGwAIABhAG4AbgB1AGEAbAAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAGUAbgB0AGUAcgBpAGMAIABmAGUAcgBtAGUAbgB0AGEAdABpAG8AbgAgAGkAbgAgAGYAZQBlAGQAbABvAHQAIABiAGUAZQBmACAAYwBhAHQAdABsAGUAXABuAEUAXwBlAG4AdABlAHIAaQBjAFwAbgB0ACAAQwBIADQAXABuAEUAXwB7AGUAbgB0AGUAcgBpAGMAfQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AagAoAEQAXwBqAFwAXAB0AGkAbQBlAHMAIABNAF8AagBcAFwAdABpAG0AZQBzACAATgBfAGoAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcAG4ARABfAGoAIAA9ACAAZAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgAG8AZgAgAGUAYQBjAGgAIABjAGEAdAB0AGwAZQAgAGwAbwB0ACAAKABkAGEAeQBzACkAXABuAE0AXwBqACAAPQAgAGQAYQBpAGwAeQAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAKABrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQApAFwAbgBOAF8AagAgAD0AIABuAHUAbQBiAGUAcgBzACAAbwBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAAaQBuACAAZQBhAGMAaAAgAGMAYQB0AHQAbABlACAAbABvAHQAIAAoAGgAZQBhAGQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEQAXwBqACwAIABNAF8AagAsACAATgBfAGoALABcAG4AIAAgACAAIAAoAEQAXwBqACAAKgAgAE0AXwBqACAAKgAgAE4AXwBqACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAbwB0AGEAbAAgAGEAbgBuAHUAYQBsACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAZQBuAHQAZQByAGkAYwAgAGYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACAAaQBuACAAZgBlAGUAZABsAG8AdAAgAGIAZQBlAGYAIABjAGEAdAB0AGwAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAGUAbgB0AGUAcgBpAGMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBIADQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBlAG4AdABlAHIAaQBjAH0APQBcAFwAcwB1AG0AXABcAG4AbwBsAGkAbQBpAHQAcwBfAGoAKABEAF8AagBcAFwAdABpAG0AZQBzACAATQBfAGoAXABcAHQAaQBtAGUAcwAgAE4AXwBqACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABfAGoAXAAiACwAIABcACIAZAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgAG8AZgAgAGUAYQBjAGgAIABjAGEAdAB0AGwAZQAgAGwAbwB0AFwAIgAsACAAXAAiAGQAYQB5AHMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAF8AagBcACIALAAgAFwAIgBkAGEAaQBsAHkAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgBcACIALAAgAFwAIgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADMALgAxAC4AMQAuADEALAAgACgAMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAF8AagBcACIALAAgAFwAIgBuAHUAbQBiAGUAcgBzACAAbwBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAAaQBuACAAZQBhAGMAaAAgAGMAYQB0AHQAbABlACAAbABvAHQAXAAiACwAIABcACIAaABlAGEAZABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBcAG4ARABhAGkAbAB5ACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAGUAbgB0AGUAcgBpAGMAIABtAGUAdABoAGEAbgBlAFwAbgBNAF8AagBcAG4AawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXABuAE0AXwBqAD0AKAA1AC4AMQAxAFwAXAB0AGkAbQBlAHMAIABJAF8AagAtADQALgAwADAAXABcAHQAaQBtAGUAcwAgAEUARQBfAGoAKwAyAC4AMgA2AFwAXAB0AGkAbQBlAHMAIABOAEQARgBfAGoAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcAG4ASQBfAGoAIAA9ACAAZAByAHkAIABtAGEAdAB0AGUAcgAgAGkAbgB0AGEAawBlACAAKABrAGcAIABEAE0ALwBoAGUAYQBkAC8AZABhAHkAKQBcAG4ARQBFAF8AagAgAD0AIABlAHQAaABlAHIAIABlAHgAdAByAGEAYwB0ACAAYQBzACAAYQAgAHAAZQByAGMAZQBuAHQAYQBnAGUAIABvAGYAIABJAF8AagAgACgAcABlAHIAIABjAGUAbgB0ACkAXABuAE4ARABGAF8AagAgAD0AIABuAGUAdQB0AHIAYQBsACAAZABlAHQAZQByAGcAZQBuAHQAIABmAGkAYgByAGUAIABhAHMAIABhACAAcABlAHIAYwBlAG4AdABhAGcAZQAgAG8AZgAgAEkAXwBqACAAKABwAGUAcgAgAGMAZQBuAHQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEkAXwBqACwAIABFAEUAXwBqACwAIABOAEQARgBfAGoALABcAG4AIAAgACAAIAAoADUALgAxADEAIAAqACAASQBfAGoAIAAtACAANAAuADAAMAAgACoAIABFAEUAXwBqACAAKwAgADIALgAyADYAIAAqACAATgBEAEYAXwBqACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEQAYQBpAGwAeQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABlAG4AdABlAHIAaQBjACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAGoAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAzAC4AMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADIAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAGwAbQBlAGkAZABhACAAZQB0ACAAYQBsAC4AIAAoADIAMAAyADUAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwBqAD0AKAA1AC4AMQAxAFwAXAB0AGkAbQBlAHMAIABJAF8AagAtADQALgAwADAAXABcAHQAaQBtAGUAcwAgAEUARQBfAGoAKwAyAC4AMgA2AFwAXAB0AGkAbQBlAHMAIABOAEQARgBfAGoAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAF8AagBcACIALAAgAFwAIgBkAHIAeQAgAG0AYQB0AHQAZQByACAAaQBuAHQAYQBrAGUAXAAiACwAIABcACIAawBnACAARABNAC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBFAF8AagBcACIALAAgAFwAIgBlAHQAaABlAHIAIABlAHgAdAByAGEAYwB0ACAAYQBzACAAYQAgAHAAZQByAGMAZQBuAHQAYQBnAGUAIABvAGYAIABJAF8AagBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEQARgBfAGoAXAAiACwAIABcACIAbgBlAHUAdAByAGEAbAAgAGQAZQB0AGUAcgBnAGUAbgB0ACAAZgBpAGIAcgBlACAAYQBzACAAYQAgAHAAZQByAGMAZQBuAHQAYQBnAGUAIABvAGYAIABJAF8AagBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgAiAH0AXQAsACIAcAByAG8AagBlAGMAdABOAGEAbQBlAHMAIgA6AFsAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVgBhAGkAcgBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADMAXwA0ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AUwB0AGEAZwBlADEATQBNAFMATwBwAHQAaQBvAG4AcwAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AUwB0AGEAZwBlADIATQBNAFMATwBwAHQAaQBvAG4AcwAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AUwB0AGEAZwBlADMATQBNAFMATwBwAHQAaQBvAG4AcwAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzAGUAcwAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAbgBpAG0AYQBsAEMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAG4AaQBtAGEAbABDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAbgBpAG0AYQBsAEMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAbgBpAG0AYQBsAEMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAbgBpAG0AYQBsAEMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARABpAGUAdABQAHIAbwBwAGUAcgB0AGkAZQBzAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAGkAZQB0AFAAcgBvAHAAZQByAHQAaQBlAHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAGkAZQB0AFAAcgBvAHAAZQByAHQAaQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARABpAGUAdABQAHIAbwBwAGUAcgB0AGkAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AQwBGAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAEMARgBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AQwBGAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AQwBGAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AQwBGAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBGAHIAYQBjAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBGAHIAYQBjAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARgByAGEAYwBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBGAHIAYQBjAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEYAcgBhAGMATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBEAGEAdABhACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEYAZQBlAGQAbABvAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARgBlAGUAZABsAG8AdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBGAGUAZQBkAGwAbwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEYAZQBlAGQAbABvAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEYAZQBlAGQAbABvAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBGAGUAZQBkAGwAbwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARgBlAGUAZABsAG8AdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARgBlAGUAZABsAG8AdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEYAZQBlAGQAbABvAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARgBlAGUAZABsAG8AdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBGAGUAZQBkAGwAbwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEYAZQBlAGQAbABvAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEYAZQBlAGQAbABvAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBGAGUAZQBkAGwAbwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARgBlAGUAZABsAG8AdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARgBlAGUAZABsAG8AdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzACIAXQAsACIAbABvAGMAYQBsAGUAIgA6AHsAIgBsAGkAcwB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAcgBvAHcAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBjAG8AbAB1AG0AbgBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUABvAHMAaQB0AGkAbwBuAHMAIgA6AFsAMwBdACwAIgBkAGUAYwBpAG0AYQBsAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiAC4AIgAsACIAZABhAHQAZQBPAHIAZABlAHIAIgA6ACIARABNAFkAIgAsACIAYwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsACIAOgAiACQAIgAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbABMAGUAYQBkACIAOgB0AHIAdQBlACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAZQBwAEIAeQBTAHAAYQBjAGUAIgA6AGYAYQBsAHMAZQAsACIAcgBvAHcATABlAHQAdABlAHIAIgA6ACIAUgAiACwAIgBjAG8AbAB1AG0AbgBMAGUAdAB0AGUAcgAiADoAIgBDACIALAAiAHIAYwBMAGUAZgB0AEIAcgBhAGMAawBlAHQAIgA6ACIAWwAiACwAIgByAGMAUgBpAGcAaAB0AEIAcgBhAGMAawBlAHQAIgA6ACIAXQAiACwAIgBzAHQAYQB0AGUAbQBlAG4AdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGwAbwBjAGEAbABlAE4AYQBtAGUAIgA6ACIAZQBuAC0AdQBzACIAfQB9AA==</AFEJSONBlob>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
@@ -23143,6 +23167,19 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBcAG4ARgByAGEAYwBXAEUAVABNAE0AUwBpACAAPQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4AKABUAGEAYgBsAGUAIABBADUALgA1AC4AMQAwAC4AMgAgAGkAcwAgAHIAZQBmAGUAcgBlAG4AYwBlAGQAIABpAG4AIABOAEkAUgAgAGIAdQB0ACAAMQAgAGkAcwAgAHUAcwBlAGQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAxACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXABuAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTACAAPQAgADAALgAwADIAIAAoAEcAZwAgAE4ALwBHAGcAIABhAHAAcABsAGkAZQBkACkAIAAoAEMAUwAgAEUARgAsACAAcwBvAHUAcgBjAGUAIABJAFAAQwBDACAAKAAyADAAMQA5ACkAKQAgAFwAbgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAIAAwAC4AMAAwADUAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsACAAMAAuADAAMAA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAgADAALgAwADAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAgADAALgAwADAANAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABjAGEAbgBlAFwAIgAsACAAMAAuADAAMQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAMAAuADAAMAA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAMAAuADAAMAA2ADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXABuAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAAVABhAGIAbABlACAANQAuADEAMgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB5AG0AYgBvAGwAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgAbQA9ADEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADIAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwAgACgAbQA9ADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAG0APQAzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGEAXAAiACwAIABcACIAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBTAHUAbQBwACAAYQBuAGQAIABkAGkAcwBwAGUAcgBzAGEAbAAgAHMAeQBzAHQAZQBtACAAKABtAD0AMwBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGIAXAAiACwAIABcACIARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAEQAcgBhAGkAbgBzACAAdABvACAAcABhAGQAZABvAGMAawAgACgAbQA9ADMAYgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIANABcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIAAoAG0APQA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA1AFwAIgAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAIAAoAG0APQA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA2AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQAgACgAbQA9ADYAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADcAXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwAgACgAbQA9ADcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADgAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgAgACgAbQA9ADgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADkAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQAgACgAbQA9ADkAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMABcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwAgACgAbQA9ADEAMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnACAAKABtAD0AMQAxACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADEAYQBcACIALAAgAFwAIgBCAGUAbAB0ACAAbQBhAG4AdQByAGUAIAByAGUAbQBvAHYAYQBsAFwAIgAsACAAXAAiAEIAZQBsAHQAIABtAGEAbgB1AHIAZQAgAHIAZQBtAG8AdgBhAGwAIAAoAG0APQAxADEAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAGIAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABzAHQAbwByAGUAZAAgAGkAbgAgAGgAbwB1AHMAZQBcACIALAAgAFwAIgBNAGEAbgB1AHIAZQAgAHMAdABvAHIAZQBkACAAaQBuACAAaABvAHUAcwBlACAAKABtAD0AMQAxAGIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAKABtAD0AMQAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADMAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAG0APQAxADMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEANABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAIAAoAG0APQAxADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBlAGUAZgAgAGMAYQB0AHQAbABlACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQB0AHQAbABlACwAIABmAG8AcgAgAG0AYQBuAHUAZgBhAGMAdAB1AHIAaQBuAGcAIABiAGUAZQBmAFwAIgAsACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBhAHQAdABsAGUALAAgAGYAbwByACAAcAByAGkAbQBlACAAYgBlAGUAZgBcACIALAAgAFwAIgBOAFMAVwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQB0AHQAbABlACwAIAB3AGUAYQBuAGUAcgBzAFwAIgAsACAAXAAiAE4AVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFEATABEAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAVABBAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBWAEkAQwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFcAQQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBDAGgAaQBjAGsAZQBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEMAaABpAGMAawBlAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBoAGkAYwBrAGUAbgBzACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQwBoAGkAYwBrAGUAbgBzAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEMAaABpAGMAawBlAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQwBoAGkAYwBrAGUAbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBDAGgAaQBjAGsAZQBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABcACIALAAgAFwAIgBTAG8AdQByAGMAZQAgAHIAZQBnAGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBoAGkAYwBrAGUAbgBzAFwAIgAsACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEQAYQBpAHIAeQBjAGEAdAB0AGwAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIABwAHIAbwBkAHUAYwB0AHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXwBWAGEAaQByAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8ARABhAGkAcgB5AGMAYQB0AHQAbABlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATABpAGYAZQBjAHkAYwBsAGUAcwAuACAAKAAyADAAMgA2ACkALgAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABHAGEAcwAgAEUAbQBpAHMAcwBpAG8AbgAgAEkAbgB0AGUAbgBzAGkAdABpAGUAcwAgAGYAbwByACAATQBhAHQAZQByAGkAYQBsACAASQBuAHAAdQB0AHMAIAB0AG8AIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAQQBnAHIAaQBjAHUAbAB0AHUAcgBlACwAIABGAGkAcwBoAGUAcgBpAGUAcwAgAGEAbgBkACAARgBvAHIAZQBzAHQAcgB5AC4AIABWAGUAcgBzAGkAbwBuACAANAA4AC4AIABkAG8AaQAgADEAMAAuADUAMgA4ADEALwB6AGUAbgBvAGQAbwAuADEAOQA2ADUANgA1ADgAMABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEQAYQBpAHIAeQBjAGEAdAB0AGwAZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AFwAIgAsACAAXAAiAFMAbwB1AHIAYwBlACAAcgBlAGcAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAaQByAHkAIABjAG8AdwBzAFwAIgAsACAAXAAiAFYASQBDAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBQAGkAZwBzACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUABpAGcAcwBfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAaQBnAHMAXAAiACwAIABcACIAQQB1AHMAdAByAGEAbABpAGEAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUwBoAGUAZQBwAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBTAGgAZQBlAHAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMAaABlAGUAcAAgAHAAcgBvAGQAdQBjAHQAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFMAaABlAGUAcABfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBTAGgAZQBlAHAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFMAaABlAGUAcABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBMAGkAZgBlAGMAeQBjAGwAZQBzAC4AIAAoADIAMAAyADYAKQAuACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEcAYQBzACAARQBtAGkAcwBzAGkAbwBuACAASQBuAHQAZQBuAHMAaQB0AGkAZQBzACAAZgBvAHIAIABNAGEAdABlAHIAaQBhAGwAIABJAG4AcAB1AHQAcwAgAHQAbwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABBAGcAcgBpAGMAdQBsAHQAdQByAGUALAAgAEYAaQBzAGgAZQByAGkAZQBzACAAYQBuAGQAIABGAG8AcgBlAHMAdAByAHkALgAgAFYAZQByAHMAaQBvAG4AIAA0ADgALgAgAGQAbwBpACAAMQAwAC4ANQAyADgAMQAvAHoAZQBuAG8AZABvAC4AMQA5ADYANQA2ADUAOAAwAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUwBoAGUAZQBwAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAaABlAGUAcAAsACAAZgBvAHIAIABtAHUAdAB0AG8AbgBcACIALAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAaABlAGUAcAAsACAAZgBvAHIAIABwAHIAaQBtAGUAIABsAGEAbQBiAFwAIgAsACAAXAAiAE4AUwBXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAUQBMAEQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBTAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFYASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAVwBBAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFIATwBXACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACAALQAgADEAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAVABhAGIAbABlAEgAZQBhAGQAZQByAEMAZQBsAGwALABcAG4AIAAgAEMATwBMAFUATQBOACgAVABhAGIAbABlAEgAZQBhAGQAZQByAEMAZQBsAGwAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIABBAHIAcgBhAHkARABhAHQAYQAsACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALAAgAFsAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQBdACwAXABuACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAASQBOAEQARQBYACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFUATgBJAFEAVQBFACgAQQByAHIAYQB5AEQAYQB0AGEAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkALAAgADEALAAgAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALAAgAFwAIgBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABJAEYAKABJAFMATgBVAE0AQgBFAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACAAIAAgACAAKQAsACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQAsACAAMAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIAAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADEAKQAqACgATABvAG8AawB1AHAAQQByAHIAYQB5ADIAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgApACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAKQApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABDAGUAbABsACwAIABEAGUAbABpAG0AaQB0AGUAcgAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQBdACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyAF0ALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSAFgATQBMACgAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMAdABcAHUAMAAwADMAZQBcAHUAMAAwADMAYwBzAFwAdQAwADAAMwBlAFwAIgAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwBzAFwAdQAwADAAMwBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgACkAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMALwB0AFwAdQAwADAAMwBlAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AZQBsAGUAdgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZQBsAGUAdgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFAARQBUAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AbQBhAHAAXwBwAGUAdAApACwAXABuACAAIAAgACAAIAAgACAAIABUAEEASwBFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAMQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATQBpAG4AQQByAHIAYQB5ACwAIABNAGEAeABBAHIAcgBhAHkALAAgAEkAdABlAG0AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBpAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGEAeABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAIABTACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUAIABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAIAAvACoAaABlAGwAcABlAHIAOgAgAGUAbgBkACAAZABhAHQAZQAgAGYAbwByACAAYQAgAHIAZQBwAG8AcgB0AGkAbgBnACAAcABlAHIAaQBvAGQAIABzAHQAYQByAHQAaQBuAGcAIABhAHQAIABhACAAZwBpAHYAZQBuACAAZABhAHQAZQAqAC8AXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALAAgAC8AKgBvAG4AbAB5ACAAbgBlAGUAZAAgAHQAbwAgAGwAbwBvAGsAIABiAGEAYwBrACAAMwA2ADUAIABkAGEAeQBzACgAbQBhAHgAIABvAHYAZQByAGwAYQBwACAAdwBpAG4AZABvAHcAKQAqAC8AXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBhACAAZQBuAGQAcwAgAGIAZQBmAG8AcgBlACAAUwAsAGkAdAAgAGMAYQBuAFwAdQAwADAAMgA3AHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQBcAHUAMAAwADMAYwBTACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGIAIABzAHQAYQByAHQAcwAgAGEAZgB0AGUAcgAgAEUALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAHAAcgBlAHYAaQBvAHUAcwAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQBcAHUAMAAwADMAZQBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbgA9ADAALABcACIAXAAiACwASABTAFQAQQBDAEsAKABzAHQAYQByAHQAcwBUAGUAeAB0ACAAXAB1ADAAMAAyADYAIABcACIAIAB0AG8AIABcACIAIABcAHUAMAAwADIANgAgAGUAbgBkAHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAdABhAGcAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlAFwAbgA9AEwAQQBNAEIARABBACgARgB1AG4AYwB0AGkAbwBuACwAIABUAEUAWABUAEIARQBGAE8AUgBFACgARgBPAFIATQBVAEwAQQBUAEUAWABUACgARgB1AG4AYwB0AGkAbwBuACkALAAgAFwAIgAoAFwAIgApACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQAsAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAD0AXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAIAA9ACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkAPQBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQA9AEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQA9AFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAgACsAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQAXAB1ADAAMAAzAGUAMAAsACAAMQAsACAAMAApAFwAbgAgACAAIAAgACkAKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAB1ADAAMAAyADcAXAAiACAAXAB1ADAAMAAyADYAIABzAGgAIABcAHUAMAAwADIANgAgAFwAIgBcAHUAMAAwADIANwAhAFwAIgAgAFwAdQAwADAAMgA2ACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBEAGkAZgBmAGUAcgBlAG4AdABTAGgAZQBlAHQAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADEAXwAyAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsACAAMQAsACAAMgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADMAXwA0AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsACAAMwAsACAANAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEcAZQB0AE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABNAE0AUwAsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAXABuACAAIAAgACAAIAAgACAAIABNAEUARABJAEEATgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVQBOAEQAKABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgADAAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0ASQBOACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBBAFgAKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATQBNAFMALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBSAGUAcwB1AGwAdABzAEkAdABlAG0ARgByAG8AbQBFAHEAdQBhAHQAaQBvAG4AVABpAHQAbABlAEEAbgBkAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABpAHQAbABlAEMAZQBsAGwALAAgAFMAbwB1AHIAYwBlAEMAZQBsAGwALABcAG4AIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgATABFAEYAVAAoAFMAbwB1AHIAYwBlAEMAZQBsAGwALAAgAEYASQBOAEQAKABcACIALABcACIALAAgAFMAbwB1AHIAYwBlAEMAZQBsAGwAKQAgAC0AMQApACwAIABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAXAAiACwAIABcACIAXAAiACkAIABcAHUAMAAwADIANgAgAFwAIgAgAFwAIgAgAFwAdQAwADAAMgA2ACAAVABpAHQAbABlAEMAZQBsAGwAXABuACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0ACIALAAiAHQAZQB4AHQAIgA6ACIALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIABsAG8AcwB0ACAAaQBuACAAdABoAGUAIABwAHIAaQBtAGEAcgB5ACAATQBNAFMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBlAGUAZABsAG8AdAAgAC0AIABGAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAGwAbwBzAHQAIABkAHUAcgBpAG4AZwAgAHMAdABvAHIAYQBnAGUAIABpAG4AIAB0AGgAZQAgAHAAcgBpAG0AYQByAHkAIABzAHkAcwB0AGUAbQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBTAEwAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAyAC4AMwAgAEMATwBOAFMAVABBAE4AVABTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANQApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAdABvACAAZQBhAGMAaAAgAHQAZQByAHQAaQBhAHIAeQAgAHMAeQBzAHQAZQBtACAAYQBzAHMAdQBtAGUAZAAgAHQAaABhAHQAIAAyACAAcABlAHIAIABjAGUAbgB0ACAAaQBzACAAcgB1AG4AIAAtACAAbwBmAGYAIABmAHIAbwBtACAAdABoAGUAIABmAGUAZQBkACAAcABhAGQALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAdABvACAAZQBhAGMAaAAgAHQAZQByAHQAaQBhAHIAeQAgAHMAeQBzAHQAZQBtACAAYQBzAHMAdQBtAGUAZAAgAHQAaABhAHQAIAAyACAAcABlAHIAIABjAGUAbgB0ACAAaQBzACAAcgB1AG4AIAAtACAAbwBmAGYAIABmAHIAbwBtACAAdABoAGUAIABmAGUAZQBkACAAcABhAGQALgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBtADEAVAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADIALgAzACAAQwBPAE4AUwBUAEEATgBUAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4AMAAyACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABcAG4AQQBzAGgAIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAbQBhAG4AdQByAGUALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAcwBoACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAG0AYQBuAHUAcgBlAC4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAyAC4AMwAgAEMATwBOAFMAVABBAE4AVABTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADEANgApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXABuAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHAAbwB0AGUAbgB0AGkAYQBsAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbAAuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEIAMABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAbQAzACAAQwBIADQAIAAvACAAawBnACAAVgBTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAyAC4AMwAgAEMATwBOAFMAVABBAE4AVABTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADEAOQApADsAXABuAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBTAHQAYQBnAGUAMQBNAE0AUwBPAHAAdABpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMQAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFMAdABhAGcAZQAyAE0ATQBTAE8AcAB0AGkAbwBuAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AIABNAE0AUwBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AUwB0AGEAZwBlADMATQBNAFMATwBwAHQAaQBvAG4AcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADEALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzAGUAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADEALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjAFwAIgA7ACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAeABwAG8AcgB0ACAAbQBpAGQAIABmAGUAZABcACIAOwAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAHgAcABvAHIAdAAgAGwAbwBuAGcAIABmAGUAZABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBcAG4AVABhAGIAbABlACAAQQAuADEALgAxAC4AMQA6ACAAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABEAHUAcgBhAHQAaQBvAG4AIABvAGYAIABzAHQAYQB5ACAAKABkAGEAeQBzACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAARAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgACgAZABhAHkAcwApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADEALgAxADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEQAdQByAGEAdABpAG8AbgAgAG8AZgAgAHMAdABhAHkAIAAoAGQAYQB5AHMAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBlAGQAbABvAHQAIAB0AHkAcABlAFwAIgAsACAAXAAiAEwAZQBuAGcAdABoACAAbwBmACAAUwB0AGEAeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjAFwAIgAsACAAXAAiADEALQA4ADAAIABkAGEAeQBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGkAZAAtAGYAZQBkAFwAIgAsACAAXAAiADgAMQAtADIAMAAwACAAZABhAHkAcwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAG4AZwAtAGYAZQBkAFwAIgAsACAAXAAiADIAMAAxACsAIABkAGEAeQBzAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAbgBpAG0AYQBsAEMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADEALgAyADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEEAbgBpAG0AYQBsACAAYwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAG4AaQBtAGEAbABDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABBAG4AaQBtAGEAbAAgAGMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAbgBpAG0AYQBsAEMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBuAGkAbQBhAGwAQwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAxAC4AMgA6ACAAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABBAG4AaQBtAGEAbAAgAGMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAbgBpAG0AYQBsAEMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AbwB2AGUAZAAgAGYAZQBlAGQAbABvAHQAIAB0AHkAcABlAHMAIAB0AG8AIABhACAAcwBlAHAAYQByAGEAdABlACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AYQBtAGUAZAAgAFwAdQAwADAAMgA3AGMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuACAALQAgAG8AcgBpAGcAaQBuAGEAbAAgAGgAYQBzACAAaABlAGEAZABlAHIAIABcAHUAMAAwADIANwBVAG4AaQB0AFwAdQAwADAAMgA3ACAAdwBoAGkAYwBoACAAYwBvAHYAZQByAHMAIAB0AHcAbwAgAGMAbwBsAHUAbQBuAHMAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBuAGkAbQBhAGwAQwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAwACwAIAA3ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAZQBkAGwAbwB0ACAAdAB5AHAAZQBcACIALAAgAFwAIgBDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAXAAiACwAIABcACIAVQBuAGkAdABcACIALAAgAFwAIgAyADAAMAA1AC0AMgAwADAAOQBcACIALAAgAFwAIgAyADAAMQAwAC0AMgAwADEANABcACIALAAgAFwAIgAyADAAMQA1AC0AMgAwADEAOQBcACIALAAgAFwAIgAyADAAMgAwAC0AMgAwADIAMwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjAFwAIgAsACAAXAAiAEQAYQB5AHMAIABvAG4AIABmAGUAZQBkAFwAIgAsACAAXAAiAGQAYQB5AHMAXAAiACwAIAA3ADAALAAgADcAMAAsACAANwAwACwAIAA3ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjAFwAIgAsACAAXAAiAEYAZQBlAGQAIABpAG4AdABhAGsAZQBcACIALAAgAFwAIgBrAGcAIABEAE0ALwBkAGEAeQBcACIALAAgADEAMAAuADAALAAgADEAMAAuADAALAAgADEAMAAuADQALAAgADEAMAAuADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjAFwAIgAsACAAXAAiAE4AIAByAGUAdABlAG4AdABpAG8AbgBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAIABvAGYAIABpAG4AdABhAGsAZQBcACIALAAgADIAMQAuADEALAAgADIAMAAuADQALAAgADIAMAAuADQALAAgADIAMAAuADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBpAGQALQBmAGUAZABcACIALAAgAFwAIgBEAGEAeQBzACAAbwBuACAAZgBlAGUAZABcACIALAAgAFwAIgBkAGEAeQBzAFwAIgAsACAAMQAxADUALAAgADEAMQA1ACwAIAAxADIAMAAsACAAMQA1ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBpAGQALQBmAGUAZABcACIALAAgAFwAIgBGAGUAZQBkACAAaQBuAHQAYQBrAGUAXAAiACwAIABcACIAawBnACAARABNAC8AZABhAHkAXAAiACwAIAAxADEALgAyACwAIAAxADAALgA4ACwAIAAxADAALgA4ACwAIAAxADAALgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBkAC0AZgBlAGQAXAAiACwAIABcACIATgAgAHIAZQB0AGUAbgB0AGkAbwBuAFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdAAgAG8AZgAgAGkAbgB0AGEAawBlAFwAIgAsACAAMQAyAC4ANQAsACAAMQAyAC4ANwAsACAAMQAyAC4ANwAsACAAMQAyAC4ANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AbgBnAC0AZgBlAGQAXAAiACwAIABcACIARABhAHkAcwAgAG8AbgAgAGYAZQBlAGQAXAAiACwAIABcACIAZABhAHkAcwBcACIALAAgADIANQAwACwAIAAyADUAMAAsACAAMgA1ADAALAAgADIANQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwBuAGcALQBmAGUAZABcACIALAAgAFwAIgBGAGUAZQBkACAAaQBuAHQAYQBrAGUAXAAiACwAIABcACIAawBnACAARABNAC8AZABhAHkAXAAiACwAIAA5AC4AMAAsACAAOAAuADUALAAgADgALgAyACwAIAA4AC4AMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AbgBnAC0AZgBlAGQAXAAiACwAIABcACIATgAgAHIAZQB0AGUAbgB0AGkAbwBuAFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdAAgAG8AZgAgAGkAbgB0AGEAawBlAFwAIgAsACAANgAuADYALAAgADcALgAwACwAIAA3AC4AMAAsACAANwAuADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARABpAGUAdABQAHIAbwBwAGUAcgB0AGkAZQBzAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADEALgAzADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEQAaQBlAHQAIABwAHIAbwBwAGUAcgB0AGkAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARABpAGUAdABQAHIAbwBwAGUAcgB0AGkAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEQAaQBlAHQAIABwAHIAbwBwAGUAcgB0AGkAZQBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADEALgAzADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEQAaQBlAHQAIABwAHIAbwBwAGUAcgB0AGkAZQBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABcAHUAMAAwADIANwBDAG8AbgB2AGUAcgB0AGUAZAAgAHQAbwAgAGYAcgBhAGMAdABpAG8AbgAgAGMAbwBsAHUAbQBuACAAYQBuAGQAIABjAG8AbgB2AGUAcgB0AGUAZAAgAE4ARABGACAAYQBuAGQAIABFAHQAaABlAHIAIABlAHgAdAByAGEAYwB0ACAAdgBhAGwAdQBlAHMAIAB0AG8AIABmAHIAYQBjAHQAaQBvAG4AcwAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AdgBlAGQAIABmAGUAZQBkAGwAbwB0ACAAdAB5AHAAZQBzACAAdABvACAAYQAgAHMAZQBwAGEAcgBhAHQAZQAgAGMAbwBsAHUAbQBuACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAGkAZQB0AFAAcgBvAHAAZQByAHQAaQBlAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAA4ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAZQBkAGwAbwB0ACAAdAB5AHAAZQBcACIALAAgAFwAIgBOAHUAdAByAGkAZQBuAHQAIABhAG4AYQBsAHkAcwBpAHMAXAAiACwAIABcACIAVQBuAGkAdABcACIALAAgAFwAIgAyADAAMAA1AC0AMgAwADAAOQBcACIALAAgAFwAIgAyADAAMQAwAC0AMgAwADEANABcACIALAAgAFwAIgAyADAAMQA1AC0AMgAwADEAOQBcACIALAAgAFwAIgAyADAAMgAwAC0AMgAwADIAMwBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgB0AGUAZAAgAHQAbwAgAGYAcgBhAGMAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjAFwAIgAsACAAXAAiAEQAcgB5ACAAbQBhAHQAdABlAHIAIABkAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5AFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgADAALgA4ADEALAAgADAALgA4ADEALAAgADAALgA4ADEALAAgADAALgA4ADEALAAgADAALgA4ADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjAFwAIgAsACAAXAAiAEMAcgB1AGQAZQAgAHAAcgBvAHQAZQBpAG4AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAMAAuADEANAAsACAAMAAuADEANAAsACAAMAAuADEANAAsACAAMAAuADEANAAsACAAMAAuADEANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAXAAiACwAIABcACIATgBEAEYAXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0AFwAIgAsACAAMgAzAC4AMAAsACAAMgAyAC4AMAAsACAAMgAyAC4AMAAsACAAMgAyAC4AMAAsACAAMAAuADIAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAXAAiACwAIABcACIARQB0AGgAZQByACAARQB4AHQAcgBhAGMAdABcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIAA0AC4ANQAsACAANAAuADUALAAgADQALgA4ACwAIAA0AC4AOAAsACAAMAAuADAANAA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBkAC0AZgBlAGQAXAAiACwAIABcACIARAByAHkAIABtAGEAdAB0AGUAcgAgAGQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAMAAuADgAMQAsACAAMAAuADgAMQAsACAAMAAuADgAMQAsACAAMAAuADgAMQAsACAAMAAuADgAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGkAZAAtAGYAZQBkAFwAIgAsACAAXAAiAEMAcgB1AGQAZQAgAHAAcgBvAHQAZQBpAG4AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAMAAuADEAMwAsACAAMAAuADEAMgA1ACwAIAAwAC4AMQAyACwAIAAwAC4AMQAyACwAIAAwAC4AMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBkAC0AZgBlAGQAXAAiACwAIABcACIATgBEAEYAXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0AFwAIgAsACAAMgA0AC4AMAAsACAAMgAyAC4AMAAsACAAMgAyAC4AMAAsACAAMgAyAC4AMAAsACAAMAAuADIAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGkAZAAtAGYAZQBkAFwAIgAsACAAXAAiAEUAdABoAGUAcgAgAEUAeAB0AHIAYQBjAHQAXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0AFwAIgAsACAANQAuADAALAAgADUALgAwACwAIAA1AC4AMAAsACAANQAuADAALAAgADAALgAwADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAG4AZwAtAEYAZQBkAFwAIgAsACAAXAAiAEQAcgB5ACAAbQBhAHQAdABlAHIAIABkAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5AFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgADAALgA4ADEALAAgADAALgA4ADEALAAgADAALgA4ADEALAAgADAALgA4ADEALAAgADAALgA4ADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAG4AZwAtAEYAZQBkAFwAIgAsACAAXAAiAEMAcgB1AGQAZQAgAHAAcgBvAHQAZQBpAG4AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAMAAuADEAMwAsACAAMAAuADEAMgA1ACwAIAAwAC4AMQAyACwAIAAwAC4AMQAyACwAIAAwAC4AMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwBuAGcALQBGAGUAZABcACIALAAgAFwAIgBOAEQARgBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIAAyADQALgAwACwAIAAyADQALgAwACwAIAAyADQALgAwACwAIAAyADQALgAwACwAIAAwAC4AMgA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwBuAGcALQBGAGUAZABcACIALAAgAFwAIgBFAHQAaABlAHIAIABFAHgAdAByAGEAYwB0AFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdABcACIALAAgADUALgAwACwAIAA1AC4AMAAsACAANQAuADUALAAgADUALgA1ACwAIAAwAC4AMAA1ADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AQwBGAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADEALgA0ADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAE0AQwBGAHMAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AVAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBDAEYAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAZQBlAGQAbABvAHQAIAAtACAATQBDAEYAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAEMARgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AQwBGAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMQAuADQAOgAgAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAATQBDAEYAcwAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQBUACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBDAEYAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAE4AUwBXACAAdgBhAGwAdQBlAHMAIABmAG8AcgAgAEEAQwBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABOAFQAIABjAG8AbAB1AG0AbgAgAHQAaABhAHQAIABkAHUAcABsAGkAYwBhAHQAZQBzACAAUQBMAEQAIAB2AGEAbAB1AGUAcwAgAGEAcwAgAHAAZQByACAAYQBkAHYAaQBjAGUAIABmAHIAbwBtACAAcwBvAHUAcgBjAGUAIABkAGEAdABhACAAcAByAG8AdgBpAGQAZQByAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAFQAQQBTACAAYwBvAGwAdQBtAG4AIAB0AGgAYQB0ACAAZAB1AHAAbABpAGMAYQB0AGUAcwAgAFYASQBDACAAdgBhAGwAdQBlAHMAIABhAHMAIABwAGUAcgAgAGEAZAB2AGkAYwBlACAAZgByAG8AbQAgAHMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHAAcgBvAHYAaQBkAGUAcgAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABcAHUAMAAwADIANwBOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABNAE0AUwAgAG4AYQBtAGUAcwAgAHQAaABhAHQAIABtAGEAdABjAGgAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAEMARgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAxADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAVABcACIALAAgAFwAIgBNAE0AUwAgAG0AXAAiACwAIABcACIATgBTAFcAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIABcACIATgBUAFwAIgAsACAAXAAiAFMAQQBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgAFwAIgBXAEEAXAAiACwAIABcACIAVABBAFMAXAAiACwAIABcACIATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAaQBtAGEAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAbABvAHQAIAAoAEYAZQBlAGQAcABhAGQAKQBcACIALAAgADAALgAwADEALAAgADAALgAwADEALAAgADAALgAwADMALAAgADAALgAwADMALAAgADAALgAwADEALAAgADAALgAwADEALAAgADAALgAwADEALAAgADAALgAwADEALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAXAAiADsAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAGMAbwBuAGQAYQByAHkAXAAiACwAIABcACIAUwBvAGwAaQBkACAAUwB0AG8AcgBhAGcAZQAgACgAUwB0AG8AYwBrAHAAaQBsAGUAKQBcACIALAAgADAALgAwADIALAAgADAALgAwADIALAAgADAALgAwADIALAAgADAALgAwADIALAAgADAALgAwADIALAAgADAALgAwADIALAAgADAALgAwADIALAAgADAALgAwADIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgA7ACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBjAG8AbgBkAGEAcgB5AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAFAAYQBzAHMAaQB2AGUAIABXAGkAbgBkAHIAbwB3ACkAXAAiACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIAOwAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGUAYwBvAG4AZABhAHIAeQBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHQAbwAgAHMAbwBpAGwAXAAiACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiADsAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAHIAdABpAGEAcgB5AFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgARQBmAGYAbAB1AGUAbgB0ACAAcABvAG4AZAApAFwAIgAsACAAMAAuADcANQAsACAAMAAuADcANQAsACAAMAAuADcANwAsACAAMAAuADcANwAsACAAMAAuADcANQAsACAAMAAuADcANQAsACAAMAAuADcANwAsACAAMAAuADcANQAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMQAuADUAOgAgAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAEUARgBzACAAKABFAEYAbQBUACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBlAGUAZABsAG8AdAAgAC0AIABOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAARQBGAHMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADEALgA1ADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABFAEYAcwAgACgARQBGAG0AVAApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgBcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuACAAdwBpAHQAaAAgAE0ATQBTACAAbgBhAG0AZQBzACAAdABoAGEAdAAgAG0AYQB0AGMAaAAgAE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAVABcACIALAAgAFwAIgBNAE0AUwAgAG0AXAAiACwAIABcACIARQBGAG0AVAAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApAFwAIgAsACAAXAAiAE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAGkAbQBhAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGwAbwB0ACAAKABGAGUAZQBkAHAAYQBkACkAXAAiACwAIAAwAC4AMAAwADUANAAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAGMAbwBuAGQAYQByAHkAXAAiACwAIABcACIAUwBvAGwAaQBkACAAUwB0AG8AcgBhAGcAZQAgACgAUwB0AG8AYwBrAHAAaQBsAGUAKQBcACIALAAgADAALgAwADAANQAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBjAG8AbgBkAGEAcgB5AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAFAAYQBzAHMAaQB2AGUAIABXAGkAbgBkAHIAbwB3ACkAXAAiACwAIAAwAC4AMAAxACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAGMAbwBuAGQAYQByAHkAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AIAB0AG8AIABzAG8AaQBsAFwAIgAsACAAMAAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAcgB0AGkAYQByAHkAXAAiACwAIABcACIAVQBuAGMAbwB2AGUAcgBlAGQAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAKABFAGYAZgBsAHUAZQBuAHQAIABQAG8AbgBkACkAXAAiACwAIAAwACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBGAHIAYQBjAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADEALgA2ADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABiAHkAIABNAE0AUwAgACgARgByAGEAYwBHAEEAUwBNAG0AVAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARgByAGEAYwBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBlAGUAZABsAG8AdAAgAC0AIABGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAYgB5ACAATQBNAFMAIAAoAEYAcgBhAGMARwBBAFMATQBtAFQAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBGAHIAYQBjAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARgByAGEAYwBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADEALgA2ADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABiAHkAIABNAE0AUwAgACgARgByAGEAYwBHAEEAUwBNAG0AVAApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEYAcgBhAGMATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAATQBNAFMAIABuAGEAbQBlAHMAIAB0AGgAYQB0ACAAbQBhAHQAYwBoACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARgByAGEAYwBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgAFQAXAAiACwAIABcACIATQBNAFMAIABtAFwAIgAsACAAXAAiAEYAcgBhAGMARwBBAFMATQBtAFQAIAAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AXAAiACwAIABcACIATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAaQBtAGEAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAbABvAHQAIAAoAEYAZQBlAGQAcABhAGQAKQBcACIALAAgADAALgA2ACwAIABcACIARAByAHkAbABvAHQAIAAoAGYAZQBlAGQAIABwAGEAZAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGUAYwBvAG4AZABhAHIAeQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlACAAKABTAHQAbwBjAGsAcABpAGwAZQApAFwAIgAsACAAMAAuADIANQAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBjAG8AbgBkAGEAcgB5AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAFAAYQBzAHMAaQB2AGUAIABXAGkAbgBkAHIAbwB3ACkAXAAiACwAIAAwAC4ANAAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBjAG8AbgBkAGEAcgB5AFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAQQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgADAALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAHIAdABpAGEAcgB5AFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgARQBmAGYAbAB1AGUAbgB0ACAAcABvAG4AZAApAFwAIgAsACAAMAAuADMANQAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEYAZQBlAGQAbABvAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMwAuADEAOgAgAEUAbgB0AGUAcgBpAGMAIABNAGUAdABoAGEAbgBlACAALQAgAEYAZQBlAGQAbABvAHQAIABCAGUAZQBmAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAzAC4AMQAuADEALgAxACAATQBlAHQAaABvAGQAIAAxACAALQAgAEUAbgB0AGUAcgBpAGMAIABCAGUAZQBmACAARgBlAGUAZABsAG8AdABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXABuAFQAbwB0AGEAbAAgAGEAbgBuAHUAYQBsACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAZQBuAHQAZQByAGkAYwAgAGYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACAAaQBuACAAZgBlAGUAZABsAG8AdAAgAGIAZQBlAGYAIABjAGEAdAB0AGwAZQBcAG4ARQBfAGUAbgB0AGUAcgBpAGMAXABuAHQAIABDAEgANABcAG4ARQBfAHsAZQBuAHQAZQByAGkAYwB9AD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBqACgARABfAGoAXABcAHQAaQBtAGUAcwAgAE0AXwBqAFwAXAB0AGkAbQBlAHMAIABOAF8AagApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBEAF8AagAgAD0AIABkAHUAcgBhAHQAaQBvAG4AIABvAGYAIABzAHQAYQB5ACAAbwBmACAAZQBhAGMAaAAgAGMAYQB0AHQAbABlACAAbABvAHQAIAAoAGQAYQB5AHMAKQBcAG4ATQBfAGoAIAA9ACAAZABhAGkAbAB5ACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIAAoAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5ACkAXABuAE4AXwBqACAAPQAgAG4AdQBtAGIAZQByAHMAIABvAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIABpAG4AIABlAGEAYwBoACAAYwBhAHQAdABsAGUAIABsAG8AdAAgACgAaABlAGEAZAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARABfAGoALAAgAE0AXwBqACwAIABOAF8AagAsAFwAbgAgACAAIAAgACgARABfAGoAIAAqACAATQBfAGoAIAAqACAATgBfAGoAKQAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABvAHQAYQBsACAAYQBuAG4AdQBhAGwAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABlAG4AdABlAHIAaQBjACAAZgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AIABpAG4AIABmAGUAZQBkAGwAbwB0ACAAYgBlAGUAZgAgAGMAYQB0AHQAbABlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AZQBuAHQAZQByAGkAYwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAEgANABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAzAC4AMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AGUAbgB0AGUAcgBpAGMAfQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AagAoAEQAXwBqAFwAXAB0AGkAbQBlAHMAIABNAF8AagBcAFwAdABpAG0AZQBzACAATgBfAGoAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAF8AagBcACIALAAgAFwAIgBkAHUAcgBhAHQAaQBvAG4AIABvAGYAIABzAHQAYQB5ACAAbwBmACAAZQBhAGMAaAAgAGMAYQB0AHQAbABlACAAbABvAHQAXAAiACwAIABcACIAZABhAHkAcwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwBqAFwAIgAsACAAXAAiAGQAYQBpAGwAeQAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuAFwAIgAsACAAXAAiAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAMwAuADEALgAxAC4AMQAsACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AXwBqAFwAIgAsACAAXAAiAG4AdQBtAGIAZQByAHMAIABvAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIABpAG4AIABlAGEAYwBoACAAYwBhAHQAdABsAGUAIABsAG8AdABcACIALAAgAFwAIgBoAGUAYQBkAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgBEAGEAaQBsAHkAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAZQBuAHQAZQByAGkAYwAgAG0AZQB0AGgAYQBuAGUAXABuAE0AXwBqAFwAbgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcAG4ATQBfAGoAPQAoADUALgAxADEAXABcAHQAaQBtAGUAcwAgAEkAXwBqAC0ANAAuADAAMABcAFwAdABpAG0AZQBzACAARQBFAF8AagArADIALgAyADYAXABcAHQAaQBtAGUAcwAgAE4ARABGAF8AagApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBJAF8AagAgAD0AIABkAHIAeQAgAG0AYQB0AHQAZQByACAAaQBuAHQAYQBrAGUAIAAoAGsAZwAgAEQATQAvAGgAZQBhAGQALwBkAGEAeQApAFwAbgBFAEUAXwBqACAAPQAgAGUAdABoAGUAcgAgAGUAeAB0AHIAYQBjAHQAIABhAHMAIABhACAAcABlAHIAYwBlAG4AdABhAGcAZQAgAG8AZgAgAEkAXwBqACAAKABwAGUAcgAgAGMAZQBuAHQAKQBcAG4ATgBEAEYAXwBqACAAPQAgAG4AZQB1AHQAcgBhAGwAIABkAGUAdABlAHIAZwBlAG4AdAAgAGYAaQBiAHIAZQAgAGEAcwAgAGEAIABwAGUAcgBjAGUAbgB0AGEAZwBlACAAbwBmACAASQBfAGoAIAAoAHAAZQByACAAYwBlAG4AdAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAASQBfAGoALAAgAEUARQBfAGoALAAgAE4ARABGAF8AagAsAFwAbgAgACAAIAAgACgANQAuADEAMQAgACoAIABJAF8AagAgAC0AIAA0AC4AMAAwACAAKgAgAEUARQBfAGoAIAArACAAMgAuADIANgAgACoAIABOAEQARgBfAGoAKQAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARABhAGkAbAB5ACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAGUAbgB0AGUAcgBpAGMAIABtAGUAdABoAGEAbgBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADMALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAbABtAGUAaQBkAGEAIABlAHQAIABhAGwALgAgACgAMgAwADIANQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAGoAPQAoADUALgAxADEAXABcAHQAaQBtAGUAcwAgAEkAXwBqAC0ANAAuADAAMABcAFwAdABpAG0AZQBzACAARQBFAF8AagArADIALgAyADYAXABcAHQAaQBtAGUAcwAgAE4ARABGAF8AagApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAXwBqAFwAIgAsACAAXAAiAGQAcgB5ACAAbQBhAHQAdABlAHIAIABpAG4AdABhAGsAZQBcACIALAAgAFwAIgBrAGcAIABEAE0ALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEUAXwBqAFwAIgAsACAAXAAiAGUAdABoAGUAcgAgAGUAeAB0AHIAYQBjAHQAIABhAHMAIABhACAAcABlAHIAYwBlAG4AdABhAGcAZQAgAG8AZgAgAEkAXwBqAFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARABGAF8AagBcACIALAAgAFwAIgBuAGUAdQB0AHIAYQBsACAAZABlAHQAZQByAGcAZQBuAHQAIABmAGkAYgByAGUAIABhAHMAIABhACAAcABlAHIAYwBlAG4AdABhAGcAZQAgAG8AZgAgAEkAXwBqAFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBWAGEAaQByAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEcAZQB0AE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBTAHQAYQBnAGUAMQBNAE0AUwBPAHAAdABpAG8AbgBzACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBTAHQAYQBnAGUAMgBNAE0AUwBPAHAAdABpAG8AbgBzACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBTAHQAYQBnAGUAMwBNAE0AUwBPAHAAdABpAG8AbgBzACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBMAGkAdgBlAHMAdABvAGMAawBDAGwAYQBzAHMAZQBzACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBuAGkAbQBhAGwAQwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAbgBpAG0AYQBsAEMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBuAGkAbQBhAGwAQwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBuAGkAbQBhAGwAQwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBuAGkAbQBhAGwAQwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAGkAZQB0AFAAcgBvAHAAZQByAHQAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAGkAZQB0AFAAcgBvAHAAZQByAHQAaQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARABpAGUAdABQAHIAbwBwAGUAcgB0AGkAZQBzAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBDAEYAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AQwBGAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBDAEYAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBDAEYAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBDAEYAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEYAcgBhAGMATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEYAcgBhAGMATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBGAHIAYQBjAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEYAcgBhAGMATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARgByAGEAYwBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAEQAYQB0AGEAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARgBlAGUAZABsAG8AdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBGAGUAZQBkAGwAbwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEYAZQBlAGQAbABvAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARgBlAGUAZABsAG8AdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARgBlAGUAZABsAG8AdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEYAZQBlAGQAbABvAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBGAGUAZQBkAGwAbwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBGAGUAZQBkAGwAbwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARgBlAGUAZABsAG8AdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBGAGUAZQBkAGwAbwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEYAZQBlAGQAbABvAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARgBlAGUAZABsAG8AdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARgBlAGUAZABsAG8AdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEYAZQBlAGQAbABvAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBGAGUAZQBkAGwAbwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBGAGUAZQBkAGwAbwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -23165,9 +23202,12 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -23181,12 +23221,9 @@
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Excel/3_1_Enteric_Feedlot_WIP_v02.prename.bak.xlsx
+++ b/Excel/3_1_Enteric_Feedlot_WIP_v02.prename.bak.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEA82253-4563-41A1-BA9B-C494BFBA0632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9CD3736-1CBA-4D9E-851F-648A9F0FA4A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="28800" windowHeight="15345" firstSheet="3" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="28800" windowHeight="15345" firstSheet="7" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="Input - Feedlot" sheetId="70" r:id="rId5"/>
     <sheet name="3.1.1.1-2 Enteric Methane" sheetId="69" r:id="rId6"/>
     <sheet name="Constants - Feedlot" sheetId="79" r:id="rId7"/>
-    <sheet name="Constants - Common" sheetId="105" r:id="rId8"/>
+    <sheet name="Constants - Common" sheetId="106" r:id="rId8"/>
     <sheet name="Constants - Livestock" sheetId="43" r:id="rId9"/>
     <sheet name="Acknowledgements" sheetId="72" r:id="rId10"/>
     <sheet name="Tab template" sheetId="74" r:id="rId11"/>
@@ -43,7 +43,17 @@
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Title">_xlfn.LAMBDA("Convert nitrous oxide emissions to carbon dioxide equivalent emissions")</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Unit">_xlfn.LAMBDA("t CO2e")</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Variable">_xlfn.LAMBDA("EN2O CO2e")</definedName>
-    <definedName name="Common_InputFunctions.Common_GetMCFTemperatureZone">_xlfn.LAMBDA(_xlpm.Temperature,_xlpm.MMS,_xlpm.TemperatureArray,_xlpm.MMSArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(MEDIAN(_xlpm.Temperature, MIN(_xlpm.TemperatureArray), MAX(_xlpm.TemperatureArray)), _xlpm.TemperatureArray, _xlfn.XLOOKUP(_xlpm.MMS, _xlpm.MMSArray, _xlpm.ReturnArray)))</definedName>
+    <definedName name="Common_InputFunctions.Common_GetMCFTemperatureZone">_xlfn.LAMBDA(_xlpm.Temperature,_xlpm.MMS,_xlpm.TemperatureArray,_xlpm.MMSArray,_xlpm.ReturnArray,
+    _xlfn.XLOOKUP(
+        MEDIAN(
+            ROUND(_xlpm.Temperature, 0),
+            MIN(_xlpm.TemperatureArray),
+            MAX(_xlpm.TemperatureArray)
+        ),
+        _xlpm.TemperatureArray,
+        _xlfn.XLOOKUP(_xlpm.MMS, _xlpm.MMSArray, _xlpm.ReturnArray)
+    )
+)</definedName>
     <definedName name="Common_InputFunctions.CommonCropping_GetFracWET">_xlfn.LAMBDA(_xlpm.LeachingZone,_xlpm.ProductionSystem,_xlpm.LeachingZoneLookup,_xlpm.LeachingZoneFracWETLookup,_xlpm.ProductionSystemLookup,_xlpm.ProductionSystemFracWETLookup, _xlfn.LET(_xlpm.LeachingZoneFracWET, Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.LeachingZone, _xlpm.LeachingZoneLookup, _xlpm.LeachingZoneFracWETLookup), _xlpm.ProductionSystemFracWET, Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.ProductionSystem, _xlpm.ProductionSystemLookup, _xlpm.ProductionSystemFracWETLookup), IF(_xlpm.LeachingZoneFracWET + _xlpm.ProductionSystemFracWET &gt; 0, 1, 0)))</definedName>
     <definedName name="Common_InputFunctions.getOverlappingReportingCycles">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
     <definedName name="Common_InputFunctions.getOverlappingReportingPeriods">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), _xlpm.n, MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1), _xlpm.yrs, _xlfn.SEQUENCE(_xlpm.n, 1, _xlpm.firstYear, 1), _xlpm.starts, DATE(_xlpm.yrs, _xlpm.m, _xlpm.d), _xlpm.ends, _xlfn.MAP(_xlpm.starts, _xlpm.PeriodEnd), _xlpm.tag, IF(_xlpm.starts = _xlpm.ReportingCycleStart, " (This reporting cycle)", ""), _xlpm.startsText, TEXT(_xlpm.starts, "dd mmm yyyy"), _xlpm.endsText, TEXT(_xlpm.ends, "dd mmm yyyy"), IF(_xlpm.n = 0, "", _xlfn.HSTACK(_xlpm.startsText &amp; " to " &amp; _xlpm.endsText &amp; _xlpm.tag))))</definedName>
@@ -59,9 +69,28 @@
     <definedName name="Common_InputFunctions.Utility_LookupN2OEFFromProdIrrigationRainfall">_xlfn.LAMBDA(_xlpm.ProductionSystem,_xlpm.IrrigationMethod,_xlpm.RainfallZone,_xlpm.ProductionSystemArray,_xlpm.IrrigationMethodArray,_xlpm.RainfallZoneArray,_xlpm.ReturnArray, _xlfn.LET(_xlpm.IrrigationMethod, IF(_xlpm.IrrigationMethod = "Not irrigated", "Not irrigated", "Any"), _xlpm.RainfallZone, IF(_xlpm.IrrigationMethod = "Not irrigated", _xlpm.RainfallZone, "Any"), _xlfn.XLOOKUP(1, (_xlpm.ProductionSystemArray = _xlpm.ProductionSystem) * (_xlpm.IrrigationMethodArray = _xlpm.IrrigationMethod) * (_xlpm.RainfallZoneArray = _xlpm.RainfallZone), _xlpm.ReturnArray)))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTable">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTableNumber">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, IF(ISNUMBER(_xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, "")), _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""), 0))</definedName>
-    <definedName name="Common_InputFunctions.Utility_LookupValueInTableOneColumnAndHeader">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray, _xlfn.XLOOKUP(_xlpm.LookupValue1, _xlpm.LookupArray1, _xlfn.XLOOKUP(_xlpm.LookupValue2, _xlpm.LookupArray2, _xlpm.ReturnArray)))</definedName>
-    <definedName name="Common_InputFunctions.Utility_LookupValueInTableTwoColumns">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray, _xlfn.XLOOKUP(1, (_xlpm.LookupArray1 = _xlpm.LookupValue1) * (_xlpm.LookupArray2 = _xlpm.LookupValue2), _xlpm.ReturnArray, ""))</definedName>
+    <definedName name="Common_InputFunctions.Utility_LookupValueInTableOneColumnAndHeader">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray,_xlop.ValueIfFalse,
+    IFERROR(
+        _xlfn.XLOOKUP(_xlpm.LookupValue1, _xlpm.LookupArray1,
+            _xlfn.XLOOKUP(_xlpm.LookupValue2, _xlpm.LookupArray2, _xlpm.ReturnArray)
+        ),
+        IF(_xlfn.ISOMITTED(_xlpm.ValueIfFalse), "", _xlpm.ValueIfFalse)
+    )
+)</definedName>
+    <definedName name="Common_InputFunctions.Utility_LookupValueInTableTwoColumns">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray,_xlop.ValueIFFalse,
+    _xlfn.XLOOKUP(1, (_xlpm.LookupArray1=_xlpm.LookupValue1)*(_xlpm.LookupArray2=_xlpm.LookupValue2), _xlpm.ReturnArray, IF(_xlfn.ISOMITTED(_xlpm.ValueIFFalse), "", _xlpm.ValueIFFalse))
+)</definedName>
+    <definedName name="Common_InputFunctions.Utility_ResultsItemFromEquationTitleAndSource">_xlfn.LAMBDA(_xlpm.TitleCell,_xlpm.SourceCell,
+    SUBSTITUTE(LEFT(_xlpm.SourceCell, FIND(",", _xlpm.SourceCell) -1), "VEERG 2026: ", "") &amp; " " &amp; _xlpm.TitleCell
+)</definedName>
     <definedName name="Common_InputFunctions.Utility_SourceHyperlink">_xlfn.LAMBDA(_xlpm.TargetCell, _xlfn.LET(_xlpm.sh, _xlfn.TEXTAFTER(CELL("filename", _xlpm.TargetCell), "]"), _xlpm.addr, CELL("address", _xlpm.TargetCell), "#'" &amp; _xlpm.sh &amp; "'!" &amp; _xlpm.addr))</definedName>
+    <definedName name="Common_InputFunctions.Utility_SourceHyperlinkDifferentSheet">_xlfn.LAMBDA(_xlpm.TargetCell,
+  _xlfn.LET(
+    _xlpm.sh, _xlfn.TEXTAFTER(CELL("filename", _xlpm.TargetCell), "]"),
+    _xlpm.addr, CELL("address", _xlpm.TargetCell),
+    "#" &amp; _xlpm.addr
+  )
+)</definedName>
     <definedName name="Common_InputFunctions.Utility_SplitStringIntoArray">_xlfn.LAMBDA(_xlpm.Cell,_xlpm.Delimiter,_xlop.CharacterToRemove1,_xlop.CharacterToRemove2, _xlfn.FILTERXML("&lt;t&gt;&lt;s&gt;" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.Cell, _xlpm.CharacterToRemove1, ""), _xlpm.CharacterToRemove2, ""), _xlpm.Delimiter, "&lt;/s&gt;&lt;s&gt;") &amp; "&lt;/s&gt;&lt;/t&gt;", "//s"))</definedName>
     <definedName name="Common_InputFunctions.Utility_SumQuantityFromCriteria">_xlfn.LAMBDA(_xlpm.Criteria1,_xlpm.Criteria1TypeArray,_xlpm.Quantity,_xlop.Multiplier,_xlop.Criteria2,_xlop.Criteria2Array, _xlfn.LET(_xlpm.multiplier, IF(_xlfn.ISOMITTED(_xlpm.Multiplier), 1, _xlpm.Multiplier), _xlpm.quantity, _xlpm.Quantity * _xlpm.multiplier, _xlpm.criteria1, --(_xlpm.Criteria1TypeArray = _xlpm.Criteria1), _xlpm.criteria2, IF(_xlfn.ISOMITTED(_xlpm.Criteria2), 1, --(_xlpm.Criteria2Array = _xlpm.Criteria2)), SUMPRODUCT(_xlpm.criteria1 * _xlpm.criteria2 * _xlpm.quantity)))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(9, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"State/Territory","Common Name","Abbreviation";"New South Wales","New South Wales","NSW";"Australian Capital Territory","ACT","ACT";"Victoria","Victoria","VIC";"Queensland","Queensland","QLD";"South Australia","South Australia","SA";"Western Australia","Western Australia","WA";"Tasmania","Tasmania","TAS";"Northern Territory","Northern Territory","NT"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -222,6 +251,61 @@
     <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Title">_xlfn.LAMBDA("Table 5.12 Additional symbols used in algorithms for manure related emissions")</definedName>
     <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Vairable">_xlfn.LAMBDA("MMS")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_BeefCattle_Data">_xlfn.LAMBDA(
+    _xlfn.MAKEARRAY(9, 2,
+      _xlfn.LAMBDA(_xlpm.r,_xlpm.c,
+        INDEX({"Product","Source region";"Cattle, for manufacturing beef","Australia";"Cattle, for prime beef","NSW";"Cattle, weaners","NT";"","QLD";"","SA";"","TAS";"","VIC";"","WA"}, _xlpm.r, _xlpm.c)
+      )
+    )
+  )</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_BeefCattle_Source">_xlfn.LAMBDA("Lifecycles. (2026). Greenhouse Gas Emission Intensities for Material Inputs to Australian Agriculture, Fisheries and Forestry. Version 48. doi 10.5281/zenodo.19656580")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_BeefCattle_Title">_xlfn.LAMBDA("Beef cattle products for scope 3")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_BeefCattle_Unit">_xlfn.LAMBDA("")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_BeefCattle_Vairable">_xlfn.LAMBDA("")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Chickens_Data">_xlfn.LAMBDA(
+    _xlfn.MAKEARRAY(2, 2,
+      _xlfn.LAMBDA(_xlpm.r,_xlpm.c,
+        INDEX({"Product","Source region";"Chickens","Australia"}, _xlpm.r, _xlpm.c)
+      )
+    )
+  )</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Chickens_Source">_xlfn.LAMBDA("Lifecycles. (2026). Greenhouse Gas Emission Intensities for Material Inputs to Australian Agriculture, Fisheries and Forestry. Version 48. doi 10.5281/zenodo.19656580")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Chickens_Title">_xlfn.LAMBDA("Chickens products for scope 3")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Chickens_Unit">_xlfn.LAMBDA("")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Chickens_Vairable">_xlfn.LAMBDA("")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Dairycattle_Data">_xlfn.LAMBDA(
+    _xlfn.MAKEARRAY(2, 2,
+      _xlfn.LAMBDA(_xlpm.r,_xlpm.c,
+        INDEX({"Product","Source region";"Dairy cows","VIC"}, _xlpm.r, _xlpm.c)
+      )
+    )
+  )</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Dairycattle_Source">_xlfn.LAMBDA("Lifecycles. (2026). Greenhouse Gas Emission Intensities for Material Inputs to Australian Agriculture, Fisheries and Forestry. Version 48. doi 10.5281/zenodo.19656580")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Dairycattle_Title">_xlfn.LAMBDA("Dairy cattle products for scope 3")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Dairycattle_Unit">_xlfn.LAMBDA("")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Dairycattle_Vairable">_xlfn.LAMBDA("")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Pigs_Data">_xlfn.LAMBDA(
+    _xlfn.MAKEARRAY(2, 2,
+      _xlfn.LAMBDA(_xlpm.r,_xlpm.c,
+        INDEX({"Product","Source region";"Pigs","Australia"}, _xlpm.r, _xlpm.c)
+      )
+    )
+  )</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Pigs_Source">_xlfn.LAMBDA("Lifecycles. (2026). Greenhouse Gas Emission Intensities for Material Inputs to Australian Agriculture, Fisheries and Forestry. Version 48. doi 10.5281/zenodo.19656580")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Pigs_Title">_xlfn.LAMBDA("Pigs products for scope 3")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Pigs_Unit">_xlfn.LAMBDA("")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Pigs_Vairable">_xlfn.LAMBDA("")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Sheep_Data">_xlfn.LAMBDA(
+    _xlfn.MAKEARRAY(8, 2,
+      _xlfn.LAMBDA(_xlpm.r,_xlpm.c,
+        INDEX({"Product","Source region";"Sheep, for mutton","Australia";"Sheep, for prime lamb","NSW";"","QLD";"","SA";"","TAS";"","VIC";"","WA"}, _xlpm.r, _xlpm.c)
+      )
+    )
+  )</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Sheep_Source">_xlfn.LAMBDA("Lifecycles. (2026). Greenhouse Gas Emission Intensities for Material Inputs to Australian Agriculture, Fisheries and Forestry. Version 48. doi 10.5281/zenodo.19656580")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Sheep_Title">_xlfn.LAMBDA("Sheep products for scope 3")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Sheep_Unit">_xlfn.LAMBDA("")</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Product_Sheep_Vairable">_xlfn.LAMBDA("")</definedName>
     <definedName name="EntericMethane_Feedlot_Equations.VEERG_3_1_1_1__1_TotalAnnualMethaneFromEntericFermentation">_xlfn.LAMBDA(_xlpm.D_j,_xlpm.M_j,_xlpm.N_j, (_xlpm.D_j * _xlpm.M_j * _xlpm.N_j) * 10 ^ -3)</definedName>
     <definedName name="EntericMethane_Feedlot_Equations.VEERG_3_1_1_1__1_TotalAnnualMethaneFromEntericFermentation_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"D_j","duration of stay of each cattle lot","days","Input";"M_j","daily methane production","kg CH4/head/day","Calculated from 3.1.1.1, (2)";"N_j","numbers of feedlot cattle in each cattle lot","head","Input"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="EntericMethane_Feedlot_Equations.VEERG_3_1_1_1__1_TotalAnnualMethaneFromEntericFermentation_LatexEquation">_xlfn.LAMBDA("E_{enteric}=\sum\nolimits_j(D_j\times M_j\times N_j)\times 10^{-3}")</definedName>
@@ -230,7 +314,9 @@
     <definedName name="EntericMethane_Feedlot_Equations.VEERG_3_1_1_1__1_TotalAnnualMethaneFromEntericFermentation_Title">_xlfn.LAMBDA("Total annual methane production from enteric fermentation in feedlot beef cattle")</definedName>
     <definedName name="EntericMethane_Feedlot_Equations.VEERG_3_1_1_1__1_TotalAnnualMethaneFromEntericFermentation_Unit">_xlfn.LAMBDA("t CH4")</definedName>
     <definedName name="EntericMethane_Feedlot_Equations.VEERG_3_1_1_1__1_TotalAnnualMethaneFromEntericFermentation_Variable">_xlfn.LAMBDA("E_enteric")</definedName>
-    <definedName name="EntericMethane_Feedlot_Equations.VEERG_3_1_1_1__2_DailyEntericMethaneProduction">_xlfn.LAMBDA(_xlpm.I_j,_xlpm.EE_j,_xlpm.NDF_j, (5.11 * _xlpm.I_j - 4 * _xlpm.EE_j + 2.26 * _xlpm.NDF_j) * 10 ^ -3)</definedName>
+    <definedName name="EntericMethane_Feedlot_Equations.VEERG_3_1_1_1__2_DailyEntericMethaneProduction">_xlfn.LAMBDA(_xlpm.I_j,_xlpm.EE_j,_xlpm.NDF_j,
+    (5.11 * _xlpm.I_j - 4 * _xlpm.EE_j + 2.26 * _xlpm.NDF_j) * 10 ^ -3
+  )</definedName>
     <definedName name="EntericMethane_Feedlot_Equations.VEERG_3_1_1_1__2_DailyEntericMethaneProduction_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"I_j","dry matter intake","kg DM/head/day","Input";"EE_j","ether extract as a percentage of I_j","per cent","Input";"NDF_j","neutral detergent fibre as a percentage of I_j","per cent","Input"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="EntericMethane_Feedlot_Equations.VEERG_3_1_1_1__2_DailyEntericMethaneProduction_LatexEquation">_xlfn.LAMBDA("M_j=(5.11\times I_j-4.00\times EE_j+2.26\times NDF_j)\times 10^{-3}")</definedName>
     <definedName name="EntericMethane_Feedlot_Equations.VEERG_3_1_1_1__2_DailyEntericMethaneProduction_NIRReference">_xlfn.LAMBDA("Almeida et al. (2025)")</definedName>
@@ -268,7 +354,13 @@
     <definedName name="M2_Table_M_j">'3.1.1.1-2 Enteric Methane'!$M$34:$O$35</definedName>
     <definedName name="M2_Table_NDF_j">'3.1.1.1-2 Enteric Methane'!$M$29:$O$30</definedName>
     <definedName name="Range_LivestockStartingValues">#REF!</definedName>
-    <definedName name="SourceData_Feedlot.SourceData_Feedlot_AnimalCharacteristics_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(10, 7, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Feedlot type","Characteristic","Unit","2005-2009","2010-2014","2015-2019","2020-2023";"Domestic","Days on feed","days",70,70,70,75;"Domestic","Feed intake","kg DM/day",10,10,10.4,10.4;"Domestic","N retention","per cent of intake",21.1,20.4,20.4,20.4;"Mid-fed","Days on feed","days",115,115,120,150;"Mid-fed","Feed intake","kg DM/day",11.2,10.8,10.8,10.8;"Mid-fed","N retention","per cent of intake",12.5,12.7,12.7,12.7;"Long-fed","Days on feed","days",250,250,250,250;"Long-fed","Feed intake","kg DM/day",9,8.5,8.2,8.2;"Long-fed","N retention","per cent of intake",6.6,7,7,7}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="SourceData_Feedlot.SourceData_Feedlot_AnimalCharacteristics_Data">_xlfn.LAMBDA(
+    _xlfn.MAKEARRAY(10, 7,
+      _xlfn.LAMBDA(_xlpm.r,_xlpm.c,
+        INDEX({"Feedlot type","Characteristic","Unit","2005-2009","2010-2014","2015-2019","2020-2023";"Domestic","Days on feed","days",70,70,70,75;"Domestic","Feed intake","kg DM/day",10,10,10.4,10.4;"Domestic","N retention","per cent of intake",21.1,20.4,20.4,20.4;"Mid-fed","Days on feed","days",115,115,120,150;"Mid-fed","Feed intake","kg DM/day",11.2,10.8,10.8,10.8;"Mid-fed","N retention","per cent of intake",12.5,12.7,12.7,12.7;"Long-fed","Days on feed","days",250,250,250,250;"Long-fed","Feed intake","kg DM/day",9,8.5,8.2,8.2;"Long-fed","N retention","per cent of intake",6.6,7,7,7}, _xlpm.r, _xlpm.c)
+      )
+    )
+  )</definedName>
     <definedName name="SourceData_Feedlot.SourceData_Feedlot_AnimalCharacteristics_Source">_xlfn.LAMBDA("VEERG 2026: Table A.1.1.2: Beef feedlot cattle - Animal characteristics")</definedName>
     <definedName name="SourceData_Feedlot.SourceData_Feedlot_AnimalCharacteristics_Title">_xlfn.LAMBDA("Beef feedlot cattle - Animal characteristics")</definedName>
     <definedName name="SourceData_Feedlot.SourceData_Feedlot_AnimalCharacteristics_Unit">_xlfn.LAMBDA("")</definedName>
@@ -279,7 +371,13 @@
     <definedName name="SourceData_Feedlot.SourceData_Feedlot_AshContent_Unit">_xlfn.LAMBDA("Fraction")</definedName>
     <definedName name="SourceData_Feedlot.SourceData_Feedlot_AshContent_Variable">_xlfn.LAMBDA("A")</definedName>
     <definedName name="SourceData_Feedlot.SourceData_Feedlot_AshContent_Variation">_xlfn.LAMBDA("")</definedName>
-    <definedName name="SourceData_Feedlot.SourceData_Feedlot_DietProperties_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(13, 8, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Feedlot type","Nutrient analysis","Unit","2005-2009","2010-2014","2015-2019","2020-2023","Converted to fraction";"Domestic","Dry matter digestibility","fraction",0.81,0.81,0.81,0.81,0.81;"Domestic","Crude protein","fraction",0.14,0.14,0.14,0.14,0.14;"Domestic","NDF","per cent",23,22,22,22,0.22;"Domestic","Ether Extract","per cent",4.5,4.5,4.8,4.8,0.048;"Mid-fed","Dry matter digestibility","fraction",0.81,0.81,0.81,0.81,0.81;"Mid-fed","Crude protein","fraction",0.13,0.125,0.12,0.12,0.12;"Mid-fed","NDF","per cent",24,22,22,22,0.22;"Mid-fed","Ether Extract","per cent",5,5,5,5,0.05;"Long-Fed","Dry matter digestibility","fraction",0.81,0.81,0.81,0.81,0.81;"Long-Fed","Crude protein","fraction",0.13,0.125,0.12,0.12,0.12;"Long-Fed","NDF","per cent",24,24,24,24,0.24;"Long-Fed","Ether Extract","per cent",5,5,5.5,5.5,0.055}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="SourceData_Feedlot.SourceData_Feedlot_DietProperties_Data">_xlfn.LAMBDA(
+    _xlfn.MAKEARRAY(13, 8,
+      _xlfn.LAMBDA(_xlpm.r,_xlpm.c,
+        INDEX({"Feedlot type","Nutrient analysis","Unit","2005-2009","2010-2014","2015-2019","2020-2023","Converted to fraction";"Domestic","Dry matter digestibility","fraction",0.81,0.81,0.81,0.81,0.81;"Domestic","Crude protein","fraction",0.14,0.14,0.14,0.14,0.14;"Domestic","NDF","per cent",23,22,22,22,0.22;"Domestic","Ether Extract","per cent",4.5,4.5,4.8,4.8,0.048;"Mid-fed","Dry matter digestibility","fraction",0.81,0.81,0.81,0.81,0.81;"Mid-fed","Crude protein","fraction",0.13,0.125,0.12,0.12,0.12;"Mid-fed","NDF","per cent",24,22,22,22,0.22;"Mid-fed","Ether Extract","per cent",5,5,5,5,0.05;"Long-Fed","Dry matter digestibility","fraction",0.81,0.81,0.81,0.81,0.81;"Long-Fed","Crude protein","fraction",0.13,0.125,0.12,0.12,0.12;"Long-Fed","NDF","per cent",24,24,24,24,0.24;"Long-Fed","Ether Extract","per cent",5,5,5.5,5.5,0.055}, _xlpm.r, _xlpm.c)
+      )
+    )
+  )</definedName>
     <definedName name="SourceData_Feedlot.SourceData_Feedlot_DietProperties_Source">_xlfn.LAMBDA("VEERG 2026: Table A.1.1.3: Beef feedlot cattle - Diet properties")</definedName>
     <definedName name="SourceData_Feedlot.SourceData_Feedlot_DietProperties_Title">_xlfn.LAMBDA("Beef feedlot cattle - Diet properties")</definedName>
     <definedName name="SourceData_Feedlot.SourceData_Feedlot_DietProperties_Unit">_xlfn.LAMBDA("")</definedName>
@@ -5989,20 +6087,20 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{514F1257-9FFD-4A06-BEB3-327873B0D4AA}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{1DAE3AF9-4DB0-43EA-BF3A-34D64DD2F967}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
   <autoFilter ref="D6:F14" xr:uid="{E0906749-7FC7-47DE-82F6-F796C4463018}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{C152B8B0-F310-4DBB-9B49-48BED2E695C2}" name="State/Territory">
+    <tableColumn id="1" xr3:uid="{A6016623-9111-4AF2-9A98-C5CB68257AED}" name="State/Territory">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{45AC8637-58DF-4872-9C96-FEB7AD6BF947}" name="Common Name">
+    <tableColumn id="2" xr3:uid="{5E996B45-8231-4D5A-9360-1969C0F60593}" name="Common Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{1BD062A5-5588-423E-A20A-B7E81A43CFA5}" name="Abbreviation">
+    <tableColumn id="3" xr3:uid="{284FD036-41D9-4465-A8B1-BE254A8E2A84}" name="Abbreviation">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6011,12 +6109,12 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{F8A6C99A-ADA3-41C7-96E2-554F9896A918}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{BF201CE5-89DA-438F-A8EE-207D01B73EEE}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
   <autoFilter ref="D20:D30" xr:uid="{5FA81339-C6C8-4D36-BEEA-6C4AEDD9E676}">
     <filterColumn colId="0" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{190049B8-689A-4E22-A7E1-A08859A5EE69}" name="SA 4 Name">
+    <tableColumn id="1" xr3:uid="{41BC2FC5-7B11-4384-A008-EAE2183B1042}" name="SA 4 Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6025,16 +6123,16 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{48DD1AAB-ABF0-45BE-B142-28C02310F073}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{3F1451BA-BCDB-44AD-BF28-0B882E6D0ED5}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
   <autoFilter ref="D36:E43" xr:uid="{B8E87A66-3E41-4AD3-925D-01EE21B43D7A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{F643D369-C343-4011-BD35-602EFB10C326}" name="Gas">
+    <tableColumn id="1" xr3:uid="{055E6137-24C0-4B23-B62F-FD7A6498CB6B}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{41AE0BEA-86C3-4EBF-BC37-B324B34EECD4}" name="CO2-e factor">
+    <tableColumn id="2" xr3:uid="{F02ABF89-4B82-4B37-A184-D27A92530E3F}" name="CO2-e factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6043,7 +6141,7 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{EC49DEDF-DE26-457F-854D-033636B33308}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{EF254599-24BB-4A60-B9F2-D5922FC18CE9}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
   <autoFilter ref="D47:H54" xr:uid="{C1F562BB-DAA6-45BB-951A-7BAFA5B64B45}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -6052,19 +6150,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{84968D2C-9FC5-4EF7-8081-E6A28FBFD3F4}" name="Gas">
+    <tableColumn id="1" xr3:uid="{C6C6B492-3C75-42E9-BDB3-383AE032C42B}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{394453BB-BE98-4169-B1E0-C08CEC806CC6}" name="Conversion factor">
+    <tableColumn id="5" xr3:uid="{36940A80-9410-4B0B-AD88-18C0ADB67E22}" name="Conversion factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{E5AE10BF-894E-49B1-987D-E45F44EF3570}" name="Conversion factor 1">
+    <tableColumn id="2" xr3:uid="{56DCEEA1-97F7-4AEF-9C87-9BD77C2D177B}" name="Conversion factor 1">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{D2B72DC8-5AEE-46A3-A04F-CC97B488C0DD}" name="Conversion factor 2">
+    <tableColumn id="3" xr3:uid="{34DAF970-C775-47E2-9B2C-F9495E6C5D28}" name="Conversion factor 2">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{C439E5B1-B5F9-42BE-87BC-8DC09F396A57}" name="Conversion factor combined">
+    <tableColumn id="4" xr3:uid="{9251D9E3-A05C-4FB8-AB84-49D33F00BF29}" name="Conversion factor combined">
       <calculatedColumnFormula>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6073,7 +6171,7 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{FB26B50D-F016-46A8-8239-55ED56246A7D}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{1F40B1C8-74D0-4C31-88BC-32D45E68D421}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
   <autoFilter ref="D89:S97" xr:uid="{5A437AE9-7724-4CF2-ACCF-291078682FB9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -6093,52 +6191,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{D60DA58E-B829-4C71-BDF8-1B2F6891D732}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{CA26A4C2-8E78-4726-BA63-698E8E0BA24B}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{27E62255-EB41-42E6-AC44-A073C3FA0BB9}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{5C268598-F274-41DA-8892-E466A9DE9497}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{3AA721EF-C414-4E64-B6AA-BA3C571C5992}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{1AD04A1C-DB01-4C9E-BCD5-B7194E2F9CB8}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{AF6C16C4-8476-41BD-9A1E-505C48CC25EA}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{2074850A-C3CC-40A3-A0AD-CDC1309207A1}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{451408CF-48F8-4DE1-BB9A-4421C30E1403}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{604BACD1-BA9D-4741-A49A-5226F77836F8}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{1623A147-4E8D-492F-89A6-638AED7900C5}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{2707F6F7-ABD9-4779-9853-3C3A79BD3181}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{385D458A-83BF-4728-A479-BF84369BF1DC}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{60BAD0EB-73A7-41FB-B23D-E22C4A268F23}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{D876EAC2-AF08-49FE-9B6C-CDE7989EFA83}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{3B193449-8EF3-4E3E-AB43-742845653363}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{B938A9A8-45AE-4A68-BCA7-9A745D70FB53}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{CD0C8DB5-3FB1-4A05-938C-8BDD89A29A58}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{653F34A5-F52E-4677-8746-13A54EBF92E6}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{7F573F67-4198-4957-8891-5C33C047C293}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{70E838A3-A75C-4F3F-81E5-6266275E71DD}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{1891836B-6B41-4C7F-91D8-5A335BB10AA7}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{978E751B-0D52-42F9-AC95-5763E6EBF7B2}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{5E313A81-3941-4684-B16D-94F55B8007EB}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{9FE8CF28-4C0B-478C-A272-F255754E1CFE}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{A2125259-D89A-4BA2-A97E-895D1223FF82}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{A0FEAB60-34BD-4B40-9475-AC3E39E73FB0}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{3C0D1B67-CFDB-4677-8F5F-4227F92A370A}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{131ECD21-599C-4EEF-A295-27CCF4A40B4C}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{ED050E57-3D91-4A80-9F61-D8917E882E4A}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{500410B2-FE3C-4B9A-9AD8-967C18CBE996}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{CE459763-6B40-4176-9360-CF9DE0130FC6}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6147,16 +6245,16 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{C6F83423-7DF4-41A5-8263-0C29E56778AC}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{85A88837-A1B7-40E5-800B-F2CF2B896C34}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
   <autoFilter ref="D63:E77" xr:uid="{3597E019-B21E-4B76-BCC8-D02D497BCFA9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{E7F87C1F-B811-4840-B256-69E32D64FFD6}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{63084658-D31E-4148-9EC5-ED4D06369357}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C5B74237-CC3F-4168-BA47-B1F2AAADA656}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{5BA22F25-94F8-435E-8656-31D9989B8C39}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6165,7 +6263,7 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{E24D4C30-636C-4DBB-912E-DE120CF69005}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{8128BB59-E877-4190-AEF6-11AD923081B8}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
   <autoFilter ref="D109:G112" xr:uid="{AB16FEAB-AB03-45E1-BBD4-66D29CD412DF}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -6173,16 +6271,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{CA52AA3C-CA89-48F3-8EB2-2A603906105F}" name="Temperature Zone">
+    <tableColumn id="1" xr3:uid="{09716885-0E03-45B9-ABFE-8BB0CC0782E5}" name="Temperature Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{A2B9AA01-382C-45E5-B91A-67D67D30AF46}" name="MAT">
+    <tableColumn id="2" xr3:uid="{3EAA9D7F-08DE-4953-B01E-F9D70456EA7E}" name="MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{3D48B33B-1F25-4CC3-8316-84653C521F29}" name="Min MAT">
+    <tableColumn id="3" xr3:uid="{DD5AC1C1-0F8D-4350-BCCC-6995CA422AE4}" name="Min MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{69582A6D-1146-4472-A3C8-1A49081BE336}" name="Max MAT">
+    <tableColumn id="4" xr3:uid="{58820687-B306-441F-8136-903608261419}" name="Max MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6191,7 +6289,7 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{58D80980-06E4-45E6-981C-63DD58B175D8}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{57081B80-7FD4-4D98-AC47-CD7543C3A035}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
   <autoFilter ref="D119:G121" xr:uid="{E08772F3-2E8C-40A8-B755-08A5BBDF4130}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -6199,16 +6297,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{7615802A-6D72-425D-9CE4-BC7D542C56CE}" name="Rainfall Zone">
+    <tableColumn id="1" xr3:uid="{69CD9BB9-2171-4E67-B9B6-21B123FA1B69}" name="Rainfall Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{E1DB465C-E06F-4F9D-A754-867F715DBD4B}" name="Annual rainfall">
+    <tableColumn id="2" xr3:uid="{33743EEB-FE0F-442C-A3C3-9090E704F6DF}" name="Annual rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{224BFC11-2477-4B45-B173-2056A7B51041}" name="Min rainfall">
+    <tableColumn id="3" xr3:uid="{FB36B090-8B4F-498F-810B-CE0F15D18335}" name="Min rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{D5E137AF-235A-4427-AC29-3E4A6DCF1833}" name="Max rainfall">
+    <tableColumn id="4" xr3:uid="{5649DC37-517D-4BB2-A59F-A5527C3DEDB9}" name="Max rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6217,16 +6315,16 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{5AB30CCE-77D5-4B5B-904A-973B0D815BBC}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{08D1CA58-8DD5-4DBD-8EC4-01FC618E4F36}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
   <autoFilter ref="D127:E129" xr:uid="{A159E140-02ED-4547-B6E1-6695D8B16A11}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{3354C849-8607-43D4-8D24-6C56D83022FA}" name="Leaching Zone">
+    <tableColumn id="1" xr3:uid="{3F856DAA-3E4F-4081-95BD-D3B18500D1FF}" name="Leaching Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{642C1800-5B0A-4D13-A1FB-D691CAD334A8}" name="Leaching criteria">
+    <tableColumn id="2" xr3:uid="{226870E2-A037-49B3-ABA5-3ACA5B6202E9}" name="Leaching criteria">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6235,16 +6333,16 @@
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="26" xr:uid="{147FB9FC-F771-4373-8260-0098BD2B1066}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{E0045FA6-FB22-4B73-AB52-0CB8D8478E4B}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
   <autoFilter ref="D153:E158" xr:uid="{133D42B0-F6D2-470A-858A-37E6A7F5EC2B}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{FC4B030D-100E-48C6-8A19-C9FFD21AD30A}" name="Data source">
+    <tableColumn id="1" xr3:uid="{2ADB1BD4-AA35-40E9-90E9-CA274C2AFE85}" name="Data source">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{ECE3A7B5-F639-4631-8963-D8108DE9E335}" name="Data score">
+    <tableColumn id="2" xr3:uid="{CF6BA90C-9C6C-458F-93C1-D259720C0C7B}" name="Data score">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6267,16 +6365,16 @@
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{1AB46D37-5755-4A18-97F3-E358B0EDC07C}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{23364BDE-6DE9-4C0C-9AC6-0A44A332C680}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
   <autoFilter ref="D134:E136" xr:uid="{308E99BE-FE1F-47A4-B2CA-97217277C4E9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{591521E2-42B6-43AE-BAF7-25FB48F19A8C}" name="Is in leaching zone">
+    <tableColumn id="1" xr3:uid="{4F389808-F31D-4034-AD4B-662900D74906}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C4E89032-2375-4FDA-A7F2-387312E8EDF8}" name="FracWET" dataDxfId="19">
+    <tableColumn id="2" xr3:uid="{7656A28A-A695-4883-9C7A-D369DE5EDA33}" name="FracWET" dataDxfId="19">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6285,7 +6383,7 @@
 </file>
 
 <file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{66045F48-BB0A-4C8D-8B03-B93E4D2C6C5B}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="34" xr:uid="{ED52A799-BC36-4B32-A233-E3C9129F3CE4}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
   <autoFilter ref="D186:H199" xr:uid="{D41FBEA4-8379-4DF7-A068-BF94D364F1A2}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -6294,19 +6392,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{B9D6B5A6-37F2-451B-BA7F-C3737937AC79}" name="Production system j">
+    <tableColumn id="1" xr3:uid="{B003EB2C-5828-45C7-939E-8B5145ED792B}" name="Production system j">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{33A93AC0-8CAF-43CC-A789-48AA6D6A0D05}" name="EFN2O">
+    <tableColumn id="2" xr3:uid="{A5C427DC-6B89-428F-B087-3D81ED2B2DE5}" name="EFN2O">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{5F09F312-EFAC-4BC4-A525-1BB6F76F6E1B}" name="Production system only">
+    <tableColumn id="3" xr3:uid="{67A034F4-B9F4-4D1E-9595-2EF20F33D947}" name="Production system only">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{0120D817-F5E6-40C1-ACC7-AC52D299FB39}" name="Irrigation method">
+    <tableColumn id="4" xr3:uid="{639E9A01-233F-4781-84B6-69EDBCB01E53}" name="Irrigation method">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{74739519-6B0E-4A93-8AEB-CFBC84040ADB}" name="Rainfall zone">
+    <tableColumn id="5" xr3:uid="{BE45B7E3-8DF9-447E-B459-CB6107838414}" name="Rainfall zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6315,16 +6413,16 @@
 </file>
 
 <file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{E2C83720-EAFA-43E0-AB96-07947352D813}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="35" xr:uid="{6BCB1B26-06C1-4B16-B564-B5DA2FA3EE94}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
   <autoFilter ref="D142:E147" xr:uid="{1F48CA34-50DE-46D5-B32A-BB3A1E818E37}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{ABE996D6-7FFF-4757-AF1E-8B8AE0A43A75}" name="Irrigation type i">
+    <tableColumn id="1" xr3:uid="{458CEC23-FEC0-40D8-B812-866FF76D299B}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{13C88F98-E76F-4886-AAD1-3AE6BFC4DCA1}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{BDB35183-26A8-47E5-8AAC-9B5F49F0249A}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6333,16 +6431,16 @@
 </file>
 
 <file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{82BDAA0A-5F7E-489B-BD52-916924A9CD66}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="36" xr:uid="{38950AFA-4B42-4A85-9EF1-7E9A1DBB35B2}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
   <autoFilter ref="D206:E208" xr:uid="{D5BE3F89-D70E-4C53-A71C-E756622DEF38}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{1EAB483F-42C3-4A45-BF25-F1A5679BA057}" name="Climate zone">
+    <tableColumn id="1" xr3:uid="{AB51473C-6B5D-4A89-B0EA-2EE4A9717B3C}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{701E9542-D730-4405-BD2C-46F9E7E9789A}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{3105ACA8-15AE-46DF-A770-9E8ECF766FB4}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6351,16 +6449,16 @@
 </file>
 
 <file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="38" xr:uid="{2C59676A-B785-468F-BA1C-C6C208F0199C}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="37" xr:uid="{93AB11C0-702F-4A17-848A-FE7B9A9459C4}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
   <autoFilter ref="D212:E224" xr:uid="{97796C3A-D95E-4077-AA20-A8FE4145DAAD}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{9125ECE9-3ADB-40B4-B531-F3DA2F54CFFB}" name="Month">
+    <tableColumn id="1" xr3:uid="{5B2F5404-B974-4598-93A5-DC5D6ED613EC}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{582A778C-7F9B-4D94-A7EC-BC86E6FCADDC}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{0A1D5F2E-D433-4351-8A33-72101DE4CBCF}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6369,7 +6467,7 @@
 </file>
 
 <file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="40" xr:uid="{BD30E199-7266-4CB7-A4BD-DD3CC4DB967D}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="39" xr:uid="{B2AA46B2-BB33-4C29-A258-DA055AD21CED}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
   <autoFilter ref="D231:S250" xr:uid="{1D72DD9B-C8FA-48F4-9A11-20231FF87B5A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -6389,52 +6487,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{0B947232-2215-4E5C-8BE6-82FC5948E9FE}" name="Temperature zone">
+    <tableColumn id="1" xr3:uid="{095A6AF7-BECB-4B91-97BB-B2F1AD0100F0}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{EEEBDDC2-30D5-4EFF-A915-8F1E0A7B846F}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{9368161D-6E38-40A3-AF02-7F24A4AE2E20}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{7217E564-89AC-487A-838A-7954E87A0B9F}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{31286F75-7812-4FB7-826F-C6EA6D7B3A91}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{33AE8184-2EB4-48C5-B874-9E826E7D1E90}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{5F630324-19F8-4733-A958-945E4F2383B6}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{313B6A18-1A3E-4A16-8CCE-B535E36BE6F1}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{32F1466D-A863-4922-9B33-79DA98CF71F9}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{47FDE51F-4140-4DF6-A107-72D5712E9140}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{44CEF460-CD2F-4921-AF52-EB64B0661EB2}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{3573E83E-46D5-48B1-BAE0-ACECC1197B12}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{18ED0545-9CE1-4290-AF36-9BEE6D9CB845}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{FC56180E-2D5D-4EFD-95AC-7A3C060EB8C1}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{0438CBCA-46BE-4B38-97BF-B1B7C5EE9330}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{A68CF33F-9F43-4652-8EF5-8A553CA12AF0}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{F384F033-CE89-4C01-97A7-29A150F4A6E6}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{5ABEE273-FA33-4A93-B1C9-3D6C1ACE4C1E}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{C3099F03-48F5-44DA-91FE-6AAE33207F41}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{9D69E8E9-80D9-4142-9C6B-E27193081B94}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{246E633E-9C1F-41A0-888C-5075CE3AF7A8}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{BDF6EE34-FC92-48F9-B9B3-4F8AF211AFD9}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{D920690F-D9F5-4734-9F91-F51129C64D9A}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{57C14148-A453-4436-9B20-4962AB8B7F03}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{C345C7B7-B4A5-471E-8467-4F6CCEAAFC4C}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{6A43489F-01AE-470A-9ED3-AF64D8A2D8BE}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{3931602C-68FB-4F72-91D6-59252A5110E2}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{2C346730-0AF9-4587-98A5-DE005A3BAC9E}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{8C6C2480-622D-47D3-81C6-3C7A0C7C9C02}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{C703CDD4-666B-4FCD-A94C-EA29E4926EC9}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{B1B7BCD7-4801-48C0-9AC3-7D11388AAFDE}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6443,16 +6541,16 @@
 </file>
 
 <file path=xl/tables/table26.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="41" xr:uid="{D66CFAC6-FEFD-4960-B662-EE72C65B775E}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="42" xr:uid="{7B80AFA6-DF04-4EC8-9824-C90ECACA11C6}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
   <autoFilter ref="D257:E259" xr:uid="{56E01C14-1BB8-4015-9158-4CEB4D3B605C}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{353E5E2B-C0FA-405D-B4AF-63E47BDD32A7}" name="Climate Zone">
+    <tableColumn id="1" xr3:uid="{94A93D00-9EBE-4F68-85E0-5A3A3742515D}" name="Climate Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{DF6D7C5F-94B7-4DCF-BABE-EE8D966EF291}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{E175E17D-948E-47D6-84F5-B05D43DFEC3A}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -18495,7 +18593,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D996979-5D34-4A3F-9D02-E3A93F8DD388}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E673B95B-C0DB-451C-A358-2843E0D0A2E6}">
   <dimension ref="A1:BY259"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -22964,6 +23062,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -23158,7 +23265,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
@@ -23169,20 +23276,19 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBcAG4ARgByAGEAYwBXAEUAVABNAE0AUwBpACAAPQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4AKABUAGEAYgBsAGUAIABBADUALgA1AC4AMQAwAC4AMgAgAGkAcwAgAHIAZQBmAGUAcgBlAG4AYwBlAGQAIABpAG4AIABOAEkAUgAgAGIAdQB0ACAAMQAgAGkAcwAgAHUAcwBlAGQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAxACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXABuAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTACAAPQAgADAALgAwADIAIAAoAEcAZwAgAE4ALwBHAGcAIABhAHAAcABsAGkAZQBkACkAIAAoAEMAUwAgAEUARgAsACAAcwBvAHUAcgBjAGUAIABJAFAAQwBDACAAKAAyADAAMQA5ACkAKQAgAFwAbgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAIAAwAC4AMAAwADUAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsACAAMAAuADAAMAA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAgADAALgAwADAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAgADAALgAwADAANAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABjAGEAbgBlAFwAIgAsACAAMAAuADAAMQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAMAAuADAAMAA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAMAAuADAAMAA2ADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXABuAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAAVABhAGIAbABlACAANQAuADEAMgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB5AG0AYgBvAGwAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgAbQA9ADEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADIAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwAgACgAbQA9ADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAG0APQAzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGEAXAAiACwAIABcACIAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBTAHUAbQBwACAAYQBuAGQAIABkAGkAcwBwAGUAcgBzAGEAbAAgAHMAeQBzAHQAZQBtACAAKABtAD0AMwBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGIAXAAiACwAIABcACIARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAEQAcgBhAGkAbgBzACAAdABvACAAcABhAGQAZABvAGMAawAgACgAbQA9ADMAYgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIANABcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIAAoAG0APQA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA1AFwAIgAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAIAAoAG0APQA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA2AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQAgACgAbQA9ADYAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADcAXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwAgACgAbQA9ADcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADgAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgAgACgAbQA9ADgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADkAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQAgACgAbQA9ADkAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMABcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwAgACgAbQA9ADEAMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnACAAKABtAD0AMQAxACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADEAYQBcACIALAAgAFwAIgBCAGUAbAB0ACAAbQBhAG4AdQByAGUAIAByAGUAbQBvAHYAYQBsAFwAIgAsACAAXAAiAEIAZQBsAHQAIABtAGEAbgB1AHIAZQAgAHIAZQBtAG8AdgBhAGwAIAAoAG0APQAxADEAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAGIAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABzAHQAbwByAGUAZAAgAGkAbgAgAGgAbwB1AHMAZQBcACIALAAgAFwAIgBNAGEAbgB1AHIAZQAgAHMAdABvAHIAZQBkACAAaQBuACAAaABvAHUAcwBlACAAKABtAD0AMQAxAGIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAKABtAD0AMQAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADMAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAG0APQAxADMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEANABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAIAAoAG0APQAxADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBlAGUAZgAgAGMAYQB0AHQAbABlACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQB0AHQAbABlACwAIABmAG8AcgAgAG0AYQBuAHUAZgBhAGMAdAB1AHIAaQBuAGcAIABiAGUAZQBmAFwAIgAsACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBhAHQAdABsAGUALAAgAGYAbwByACAAcAByAGkAbQBlACAAYgBlAGUAZgBcACIALAAgAFwAIgBOAFMAVwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQB0AHQAbABlACwAIAB3AGUAYQBuAGUAcgBzAFwAIgAsACAAXAAiAE4AVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFEATABEAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAVABBAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBWAEkAQwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFcAQQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBDAGgAaQBjAGsAZQBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEMAaABpAGMAawBlAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBoAGkAYwBrAGUAbgBzACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQwBoAGkAYwBrAGUAbgBzAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEMAaABpAGMAawBlAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQwBoAGkAYwBrAGUAbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBDAGgAaQBjAGsAZQBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABcACIALAAgAFwAIgBTAG8AdQByAGMAZQAgAHIAZQBnAGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBoAGkAYwBrAGUAbgBzAFwAIgAsACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEQAYQBpAHIAeQBjAGEAdAB0AGwAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIABwAHIAbwBkAHUAYwB0AHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXwBWAGEAaQByAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8ARABhAGkAcgB5AGMAYQB0AHQAbABlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATABpAGYAZQBjAHkAYwBsAGUAcwAuACAAKAAyADAAMgA2ACkALgAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABHAGEAcwAgAEUAbQBpAHMAcwBpAG8AbgAgAEkAbgB0AGUAbgBzAGkAdABpAGUAcwAgAGYAbwByACAATQBhAHQAZQByAGkAYQBsACAASQBuAHAAdQB0AHMAIAB0AG8AIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAQQBnAHIAaQBjAHUAbAB0AHUAcgBlACwAIABGAGkAcwBoAGUAcgBpAGUAcwAgAGEAbgBkACAARgBvAHIAZQBzAHQAcgB5AC4AIABWAGUAcgBzAGkAbwBuACAANAA4AC4AIABkAG8AaQAgADEAMAAuADUAMgA4ADEALwB6AGUAbgBvAGQAbwAuADEAOQA2ADUANgA1ADgAMABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEQAYQBpAHIAeQBjAGEAdAB0AGwAZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AFwAIgAsACAAXAAiAFMAbwB1AHIAYwBlACAAcgBlAGcAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAaQByAHkAIABjAG8AdwBzAFwAIgAsACAAXAAiAFYASQBDAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBQAGkAZwBzACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUABpAGcAcwBfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAaQBnAHMAXAAiACwAIABcACIAQQB1AHMAdAByAGEAbABpAGEAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUwBoAGUAZQBwAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBTAGgAZQBlAHAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMAaABlAGUAcAAgAHAAcgBvAGQAdQBjAHQAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFMAaABlAGUAcABfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBTAGgAZQBlAHAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFMAaABlAGUAcABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBMAGkAZgBlAGMAeQBjAGwAZQBzAC4AIAAoADIAMAAyADYAKQAuACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEcAYQBzACAARQBtAGkAcwBzAGkAbwBuACAASQBuAHQAZQBuAHMAaQB0AGkAZQBzACAAZgBvAHIAIABNAGEAdABlAHIAaQBhAGwAIABJAG4AcAB1AHQAcwAgAHQAbwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABBAGcAcgBpAGMAdQBsAHQAdQByAGUALAAgAEYAaQBzAGgAZQByAGkAZQBzACAAYQBuAGQAIABGAG8AcgBlAHMAdAByAHkALgAgAFYAZQByAHMAaQBvAG4AIAA0ADgALgAgAGQAbwBpACAAMQAwAC4ANQAyADgAMQAvAHoAZQBuAG8AZABvAC4AMQA5ADYANQA2ADUAOAAwAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUwBoAGUAZQBwAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAaABlAGUAcAAsACAAZgBvAHIAIABtAHUAdAB0AG8AbgBcACIALAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAaABlAGUAcAAsACAAZgBvAHIAIABwAHIAaQBtAGUAIABsAGEAbQBiAFwAIgAsACAAXAAiAE4AUwBXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAUQBMAEQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBTAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFYASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAVwBBAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFIATwBXACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACAALQAgADEAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAVABhAGIAbABlAEgAZQBhAGQAZQByAEMAZQBsAGwALABcAG4AIAAgAEMATwBMAFUATQBOACgAVABhAGIAbABlAEgAZQBhAGQAZQByAEMAZQBsAGwAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIABBAHIAcgBhAHkARABhAHQAYQAsACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALAAgAFsAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQBdACwAXABuACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAASQBOAEQARQBYACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFUATgBJAFEAVQBFACgAQQByAHIAYQB5AEQAYQB0AGEAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkALAAgADEALAAgAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALAAgAFwAIgBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABJAEYAKABJAFMATgBVAE0AQgBFAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACAAIAAgACAAKQAsACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQAsACAAMAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIAAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADEAKQAqACgATABvAG8AawB1AHAAQQByAHIAYQB5ADIAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgApACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAKQApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABDAGUAbABsACwAIABEAGUAbABpAG0AaQB0AGUAcgAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQBdACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyAF0ALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSAFgATQBMACgAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMAdABcAHUAMAAwADMAZQBcAHUAMAAwADMAYwBzAFwAdQAwADAAMwBlAFwAIgAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwBzAFwAdQAwADAAMwBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgACkAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMALwB0AFwAdQAwADAAMwBlAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AZQBsAGUAdgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZQBsAGUAdgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFAARQBUAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AbQBhAHAAXwBwAGUAdAApACwAXABuACAAIAAgACAAIAAgACAAIABUAEEASwBFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAMQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATQBpAG4AQQByAHIAYQB5ACwAIABNAGEAeABBAHIAcgBhAHkALAAgAEkAdABlAG0AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBpAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGEAeABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAIABTACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUAIABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAIAAvACoAaABlAGwAcABlAHIAOgAgAGUAbgBkACAAZABhAHQAZQAgAGYAbwByACAAYQAgAHIAZQBwAG8AcgB0AGkAbgBnACAAcABlAHIAaQBvAGQAIABzAHQAYQByAHQAaQBuAGcAIABhAHQAIABhACAAZwBpAHYAZQBuACAAZABhAHQAZQAqAC8AXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALAAgAC8AKgBvAG4AbAB5ACAAbgBlAGUAZAAgAHQAbwAgAGwAbwBvAGsAIABiAGEAYwBrACAAMwA2ADUAIABkAGEAeQBzACgAbQBhAHgAIABvAHYAZQByAGwAYQBwACAAdwBpAG4AZABvAHcAKQAqAC8AXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBhACAAZQBuAGQAcwAgAGIAZQBmAG8AcgBlACAAUwAsAGkAdAAgAGMAYQBuAFwAdQAwADAAMgA3AHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQBcAHUAMAAwADMAYwBTACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGIAIABzAHQAYQByAHQAcwAgAGEAZgB0AGUAcgAgAEUALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAHAAcgBlAHYAaQBvAHUAcwAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQBcAHUAMAAwADMAZQBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbgA9ADAALABcACIAXAAiACwASABTAFQAQQBDAEsAKABzAHQAYQByAHQAcwBUAGUAeAB0ACAAXAB1ADAAMAAyADYAIABcACIAIAB0AG8AIABcACIAIABcAHUAMAAwADIANgAgAGUAbgBkAHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAdABhAGcAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlAFwAbgA9AEwAQQBNAEIARABBACgARgB1AG4AYwB0AGkAbwBuACwAIABUAEUAWABUAEIARQBGAE8AUgBFACgARgBPAFIATQBVAEwAQQBUAEUAWABUACgARgB1AG4AYwB0AGkAbwBuACkALAAgAFwAIgAoAFwAIgApACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQAsAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAD0AXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAIAA9ACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkAPQBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQA9AEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQA9AFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAgACsAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQAXAB1ADAAMAAzAGUAMAAsACAAMQAsACAAMAApAFwAbgAgACAAIAAgACkAKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAB1ADAAMAAyADcAXAAiACAAXAB1ADAAMAAyADYAIABzAGgAIABcAHUAMAAwADIANgAgAFwAIgBcAHUAMAAwADIANwAhAFwAIgAgAFwAdQAwADAAMgA2ACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBEAGkAZgBmAGUAcgBlAG4AdABTAGgAZQBlAHQAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADEAXwAyAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsACAAMQAsACAAMgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADMAXwA0AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsACAAMwAsACAANAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEcAZQB0AE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABNAE0AUwAsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAXABuACAAIAAgACAAIAAgACAAIABNAEUARABJAEEATgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVQBOAEQAKABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgADAAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0ASQBOACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBBAFgAKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATQBNAFMALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBSAGUAcwB1AGwAdABzAEkAdABlAG0ARgByAG8AbQBFAHEAdQBhAHQAaQBvAG4AVABpAHQAbABlAEEAbgBkAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABpAHQAbABlAEMAZQBsAGwALAAgAFMAbwB1AHIAYwBlAEMAZQBsAGwALABcAG4AIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgATABFAEYAVAAoAFMAbwB1AHIAYwBlAEMAZQBsAGwALAAgAEYASQBOAEQAKABcACIALABcACIALAAgAFMAbwB1AHIAYwBlAEMAZQBsAGwAKQAgAC0AMQApACwAIABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAXAAiACwAIABcACIAXAAiACkAIABcAHUAMAAwADIANgAgAFwAIgAgAFwAIgAgAFwAdQAwADAAMgA2ACAAVABpAHQAbABlAEMAZQBsAGwAXABuACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0ACIALAAiAHQAZQB4AHQAIgA6ACIALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIABsAG8AcwB0ACAAaQBuACAAdABoAGUAIABwAHIAaQBtAGEAcgB5ACAATQBNAFMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBlAGUAZABsAG8AdAAgAC0AIABGAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAGwAbwBzAHQAIABkAHUAcgBpAG4AZwAgAHMAdABvAHIAYQBnAGUAIABpAG4AIAB0AGgAZQAgAHAAcgBpAG0AYQByAHkAIABzAHkAcwB0AGUAbQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBTAEwAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAyAC4AMwAgAEMATwBOAFMAVABBAE4AVABTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANQApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAdABvACAAZQBhAGMAaAAgAHQAZQByAHQAaQBhAHIAeQAgAHMAeQBzAHQAZQBtACAAYQBzAHMAdQBtAGUAZAAgAHQAaABhAHQAIAAyACAAcABlAHIAIABjAGUAbgB0ACAAaQBzACAAcgB1AG4AIAAtACAAbwBmAGYAIABmAHIAbwBtACAAdABoAGUAIABmAGUAZQBkACAAcABhAGQALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAdABvACAAZQBhAGMAaAAgAHQAZQByAHQAaQBhAHIAeQAgAHMAeQBzAHQAZQBtACAAYQBzAHMAdQBtAGUAZAAgAHQAaABhAHQAIAAyACAAcABlAHIAIABjAGUAbgB0ACAAaQBzACAAcgB1AG4AIAAtACAAbwBmAGYAIABmAHIAbwBtACAAdABoAGUAIABmAGUAZQBkACAAcABhAGQALgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBtADEAVAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADIALgAzACAAQwBPAE4AUwBUAEEATgBUAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4AMAAyACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABcAG4AQQBzAGgAIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAbQBhAG4AdQByAGUALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAcwBoACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAG0AYQBuAHUAcgBlAC4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAyAC4AMwAgAEMATwBOAFMAVABBAE4AVABTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADEANgApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXABuAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHAAbwB0AGUAbgB0AGkAYQBsAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbAAuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEIAMABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAbQAzACAAQwBIADQAIAAvACAAawBnACAAVgBTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAyAC4AMwAgAEMATwBOAFMAVABBAE4AVABTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADEAOQApADsAXABuAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBTAHQAYQBnAGUAMQBNAE0AUwBPAHAAdABpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMQAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFMAdABhAGcAZQAyAE0ATQBTAE8AcAB0AGkAbwBuAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AIABNAE0AUwBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AUwB0AGEAZwBlADMATQBNAFMATwBwAHQAaQBvAG4AcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADEALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzAGUAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADEALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjAFwAIgA7ACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAeABwAG8AcgB0ACAAbQBpAGQAIABmAGUAZABcACIAOwAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAHgAcABvAHIAdAAgAGwAbwBuAGcAIABmAGUAZABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBcAG4AVABhAGIAbABlACAAQQAuADEALgAxAC4AMQA6ACAAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABEAHUAcgBhAHQAaQBvAG4AIABvAGYAIABzAHQAYQB5ACAAKABkAGEAeQBzACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAARAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgACgAZABhAHkAcwApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADEALgAxADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEQAdQByAGEAdABpAG8AbgAgAG8AZgAgAHMAdABhAHkAIAAoAGQAYQB5AHMAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBlAGQAbABvAHQAIAB0AHkAcABlAFwAIgAsACAAXAAiAEwAZQBuAGcAdABoACAAbwBmACAAUwB0AGEAeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjAFwAIgAsACAAXAAiADEALQA4ADAAIABkAGEAeQBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGkAZAAtAGYAZQBkAFwAIgAsACAAXAAiADgAMQAtADIAMAAwACAAZABhAHkAcwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAG4AZwAtAGYAZQBkAFwAIgAsACAAXAAiADIAMAAxACsAIABkAGEAeQBzAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAbgBpAG0AYQBsAEMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADEALgAyADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEEAbgBpAG0AYQBsACAAYwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAG4AaQBtAGEAbABDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABBAG4AaQBtAGEAbAAgAGMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAbgBpAG0AYQBsAEMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBuAGkAbQBhAGwAQwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAxAC4AMgA6ACAAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABBAG4AaQBtAGEAbAAgAGMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAbgBpAG0AYQBsAEMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AbwB2AGUAZAAgAGYAZQBlAGQAbABvAHQAIAB0AHkAcABlAHMAIAB0AG8AIABhACAAcwBlAHAAYQByAGEAdABlACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AYQBtAGUAZAAgAFwAdQAwADAAMgA3AGMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuACAALQAgAG8AcgBpAGcAaQBuAGEAbAAgAGgAYQBzACAAaABlAGEAZABlAHIAIABcAHUAMAAwADIANwBVAG4AaQB0AFwAdQAwADAAMgA3ACAAdwBoAGkAYwBoACAAYwBvAHYAZQByAHMAIAB0AHcAbwAgAGMAbwBsAHUAbQBuAHMAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBuAGkAbQBhAGwAQwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAwACwAIAA3ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAZQBkAGwAbwB0ACAAdAB5AHAAZQBcACIALAAgAFwAIgBDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAXAAiACwAIABcACIAVQBuAGkAdABcACIALAAgAFwAIgAyADAAMAA1AC0AMgAwADAAOQBcACIALAAgAFwAIgAyADAAMQAwAC0AMgAwADEANABcACIALAAgAFwAIgAyADAAMQA1AC0AMgAwADEAOQBcACIALAAgAFwAIgAyADAAMgAwAC0AMgAwADIAMwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjAFwAIgAsACAAXAAiAEQAYQB5AHMAIABvAG4AIABmAGUAZQBkAFwAIgAsACAAXAAiAGQAYQB5AHMAXAAiACwAIAA3ADAALAAgADcAMAAsACAANwAwACwAIAA3ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjAFwAIgAsACAAXAAiAEYAZQBlAGQAIABpAG4AdABhAGsAZQBcACIALAAgAFwAIgBrAGcAIABEAE0ALwBkAGEAeQBcACIALAAgADEAMAAuADAALAAgADEAMAAuADAALAAgADEAMAAuADQALAAgADEAMAAuADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjAFwAIgAsACAAXAAiAE4AIAByAGUAdABlAG4AdABpAG8AbgBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAIABvAGYAIABpAG4AdABhAGsAZQBcACIALAAgADIAMQAuADEALAAgADIAMAAuADQALAAgADIAMAAuADQALAAgADIAMAAuADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBpAGQALQBmAGUAZABcACIALAAgAFwAIgBEAGEAeQBzACAAbwBuACAAZgBlAGUAZABcACIALAAgAFwAIgBkAGEAeQBzAFwAIgAsACAAMQAxADUALAAgADEAMQA1ACwAIAAxADIAMAAsACAAMQA1ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBpAGQALQBmAGUAZABcACIALAAgAFwAIgBGAGUAZQBkACAAaQBuAHQAYQBrAGUAXAAiACwAIABcACIAawBnACAARABNAC8AZABhAHkAXAAiACwAIAAxADEALgAyACwAIAAxADAALgA4ACwAIAAxADAALgA4ACwAIAAxADAALgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBkAC0AZgBlAGQAXAAiACwAIABcACIATgAgAHIAZQB0AGUAbgB0AGkAbwBuAFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdAAgAG8AZgAgAGkAbgB0AGEAawBlAFwAIgAsACAAMQAyAC4ANQAsACAAMQAyAC4ANwAsACAAMQAyAC4ANwAsACAAMQAyAC4ANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AbgBnAC0AZgBlAGQAXAAiACwAIABcACIARABhAHkAcwAgAG8AbgAgAGYAZQBlAGQAXAAiACwAIABcACIAZABhAHkAcwBcACIALAAgADIANQAwACwAIAAyADUAMAAsACAAMgA1ADAALAAgADIANQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwBuAGcALQBmAGUAZABcACIALAAgAFwAIgBGAGUAZQBkACAAaQBuAHQAYQBrAGUAXAAiACwAIABcACIAawBnACAARABNAC8AZABhAHkAXAAiACwAIAA5AC4AMAAsACAAOAAuADUALAAgADgALgAyACwAIAA4AC4AMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AbgBnAC0AZgBlAGQAXAAiACwAIABcACIATgAgAHIAZQB0AGUAbgB0AGkAbwBuAFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdAAgAG8AZgAgAGkAbgB0AGEAawBlAFwAIgAsACAANgAuADYALAAgADcALgAwACwAIAA3AC4AMAAsACAANwAuADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARABpAGUAdABQAHIAbwBwAGUAcgB0AGkAZQBzAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADEALgAzADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEQAaQBlAHQAIABwAHIAbwBwAGUAcgB0AGkAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARABpAGUAdABQAHIAbwBwAGUAcgB0AGkAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEQAaQBlAHQAIABwAHIAbwBwAGUAcgB0AGkAZQBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADEALgAzADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEQAaQBlAHQAIABwAHIAbwBwAGUAcgB0AGkAZQBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABcAHUAMAAwADIANwBDAG8AbgB2AGUAcgB0AGUAZAAgAHQAbwAgAGYAcgBhAGMAdABpAG8AbgAgAGMAbwBsAHUAbQBuACAAYQBuAGQAIABjAG8AbgB2AGUAcgB0AGUAZAAgAE4ARABGACAAYQBuAGQAIABFAHQAaABlAHIAIABlAHgAdAByAGEAYwB0ACAAdgBhAGwAdQBlAHMAIAB0AG8AIABmAHIAYQBjAHQAaQBvAG4AcwAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AdgBlAGQAIABmAGUAZQBkAGwAbwB0ACAAdAB5AHAAZQBzACAAdABvACAAYQAgAHMAZQBwAGEAcgBhAHQAZQAgAGMAbwBsAHUAbQBuACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAGkAZQB0AFAAcgBvAHAAZQByAHQAaQBlAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAA4ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAZQBkAGwAbwB0ACAAdAB5AHAAZQBcACIALAAgAFwAIgBOAHUAdAByAGkAZQBuAHQAIABhAG4AYQBsAHkAcwBpAHMAXAAiACwAIABcACIAVQBuAGkAdABcACIALAAgAFwAIgAyADAAMAA1AC0AMgAwADAAOQBcACIALAAgAFwAIgAyADAAMQAwAC0AMgAwADEANABcACIALAAgAFwAIgAyADAAMQA1AC0AMgAwADEAOQBcACIALAAgAFwAIgAyADAAMgAwAC0AMgAwADIAMwBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgB0AGUAZAAgAHQAbwAgAGYAcgBhAGMAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjAFwAIgAsACAAXAAiAEQAcgB5ACAAbQBhAHQAdABlAHIAIABkAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5AFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgADAALgA4ADEALAAgADAALgA4ADEALAAgADAALgA4ADEALAAgADAALgA4ADEALAAgADAALgA4ADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjAFwAIgAsACAAXAAiAEMAcgB1AGQAZQAgAHAAcgBvAHQAZQBpAG4AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAMAAuADEANAAsACAAMAAuADEANAAsACAAMAAuADEANAAsACAAMAAuADEANAAsACAAMAAuADEANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAXAAiACwAIABcACIATgBEAEYAXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0AFwAIgAsACAAMgAzAC4AMAAsACAAMgAyAC4AMAAsACAAMgAyAC4AMAAsACAAMgAyAC4AMAAsACAAMAAuADIAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAXAAiACwAIABcACIARQB0AGgAZQByACAARQB4AHQAcgBhAGMAdABcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIAA0AC4ANQAsACAANAAuADUALAAgADQALgA4ACwAIAA0AC4AOAAsACAAMAAuADAANAA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBkAC0AZgBlAGQAXAAiACwAIABcACIARAByAHkAIABtAGEAdAB0AGUAcgAgAGQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAMAAuADgAMQAsACAAMAAuADgAMQAsACAAMAAuADgAMQAsACAAMAAuADgAMQAsACAAMAAuADgAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGkAZAAtAGYAZQBkAFwAIgAsACAAXAAiAEMAcgB1AGQAZQAgAHAAcgBvAHQAZQBpAG4AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAMAAuADEAMwAsACAAMAAuADEAMgA1ACwAIAAwAC4AMQAyACwAIAAwAC4AMQAyACwAIAAwAC4AMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBkAC0AZgBlAGQAXAAiACwAIABcACIATgBEAEYAXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0AFwAIgAsACAAMgA0AC4AMAAsACAAMgAyAC4AMAAsACAAMgAyAC4AMAAsACAAMgAyAC4AMAAsACAAMAAuADIAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGkAZAAtAGYAZQBkAFwAIgAsACAAXAAiAEUAdABoAGUAcgAgAEUAeAB0AHIAYQBjAHQAXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0AFwAIgAsACAANQAuADAALAAgADUALgAwACwAIAA1AC4AMAAsACAANQAuADAALAAgADAALgAwADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAG4AZwAtAEYAZQBkAFwAIgAsACAAXAAiAEQAcgB5ACAAbQBhAHQAdABlAHIAIABkAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5AFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgADAALgA4ADEALAAgADAALgA4ADEALAAgADAALgA4ADEALAAgADAALgA4ADEALAAgADAALgA4ADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAG4AZwAtAEYAZQBkAFwAIgAsACAAXAAiAEMAcgB1AGQAZQAgAHAAcgBvAHQAZQBpAG4AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAMAAuADEAMwAsACAAMAAuADEAMgA1ACwAIAAwAC4AMQAyACwAIAAwAC4AMQAyACwAIAAwAC4AMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwBuAGcALQBGAGUAZABcACIALAAgAFwAIgBOAEQARgBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIAAyADQALgAwACwAIAAyADQALgAwACwAIAAyADQALgAwACwAIAAyADQALgAwACwAIAAwAC4AMgA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwBuAGcALQBGAGUAZABcACIALAAgAFwAIgBFAHQAaABlAHIAIABFAHgAdAByAGEAYwB0AFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdABcACIALAAgADUALgAwACwAIAA1AC4AMAAsACAANQAuADUALAAgADUALgA1ACwAIAAwAC4AMAA1ADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AQwBGAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADEALgA0ADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAE0AQwBGAHMAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AVAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBDAEYAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAZQBlAGQAbABvAHQAIAAtACAATQBDAEYAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAEMARgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AQwBGAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMQAuADQAOgAgAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAATQBDAEYAcwAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQBUACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBDAEYAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAE4AUwBXACAAdgBhAGwAdQBlAHMAIABmAG8AcgAgAEEAQwBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABOAFQAIABjAG8AbAB1AG0AbgAgAHQAaABhAHQAIABkAHUAcABsAGkAYwBhAHQAZQBzACAAUQBMAEQAIAB2AGEAbAB1AGUAcwAgAGEAcwAgAHAAZQByACAAYQBkAHYAaQBjAGUAIABmAHIAbwBtACAAcwBvAHUAcgBjAGUAIABkAGEAdABhACAAcAByAG8AdgBpAGQAZQByAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAFQAQQBTACAAYwBvAGwAdQBtAG4AIAB0AGgAYQB0ACAAZAB1AHAAbABpAGMAYQB0AGUAcwAgAFYASQBDACAAdgBhAGwAdQBlAHMAIABhAHMAIABwAGUAcgAgAGEAZAB2AGkAYwBlACAAZgByAG8AbQAgAHMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHAAcgBvAHYAaQBkAGUAcgAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABcAHUAMAAwADIANwBOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABNAE0AUwAgAG4AYQBtAGUAcwAgAHQAaABhAHQAIABtAGEAdABjAGgAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAEMARgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAxADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAVABcACIALAAgAFwAIgBNAE0AUwAgAG0AXAAiACwAIABcACIATgBTAFcAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIABcACIATgBUAFwAIgAsACAAXAAiAFMAQQBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgAFwAIgBXAEEAXAAiACwAIABcACIAVABBAFMAXAAiACwAIABcACIATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAaQBtAGEAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAbABvAHQAIAAoAEYAZQBlAGQAcABhAGQAKQBcACIALAAgADAALgAwADEALAAgADAALgAwADEALAAgADAALgAwADMALAAgADAALgAwADMALAAgADAALgAwADEALAAgADAALgAwADEALAAgADAALgAwADEALAAgADAALgAwADEALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAXAAiADsAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAGMAbwBuAGQAYQByAHkAXAAiACwAIABcACIAUwBvAGwAaQBkACAAUwB0AG8AcgBhAGcAZQAgACgAUwB0AG8AYwBrAHAAaQBsAGUAKQBcACIALAAgADAALgAwADIALAAgADAALgAwADIALAAgADAALgAwADIALAAgADAALgAwADIALAAgADAALgAwADIALAAgADAALgAwADIALAAgADAALgAwADIALAAgADAALgAwADIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgA7ACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBjAG8AbgBkAGEAcgB5AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAFAAYQBzAHMAaQB2AGUAIABXAGkAbgBkAHIAbwB3ACkAXAAiACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIAOwAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGUAYwBvAG4AZABhAHIAeQBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHQAbwAgAHMAbwBpAGwAXAAiACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiADsAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAHIAdABpAGEAcgB5AFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgARQBmAGYAbAB1AGUAbgB0ACAAcABvAG4AZAApAFwAIgAsACAAMAAuADcANQAsACAAMAAuADcANQAsACAAMAAuADcANwAsACAAMAAuADcANwAsACAAMAAuADcANQAsACAAMAAuADcANQAsACAAMAAuADcANwAsACAAMAAuADcANQAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMQAuADUAOgAgAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAEUARgBzACAAKABFAEYAbQBUACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBlAGUAZABsAG8AdAAgAC0AIABOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAARQBGAHMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADEALgA1ADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABFAEYAcwAgACgARQBGAG0AVAApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgBcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuACAAdwBpAHQAaAAgAE0ATQBTACAAbgBhAG0AZQBzACAAdABoAGEAdAAgAG0AYQB0AGMAaAAgAE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAVABcACIALAAgAFwAIgBNAE0AUwAgAG0AXAAiACwAIABcACIARQBGAG0AVAAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApAFwAIgAsACAAXAAiAE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAGkAbQBhAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGwAbwB0ACAAKABGAGUAZQBkAHAAYQBkACkAXAAiACwAIAAwAC4AMAAwADUANAAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAGMAbwBuAGQAYQByAHkAXAAiACwAIABcACIAUwBvAGwAaQBkACAAUwB0AG8AcgBhAGcAZQAgACgAUwB0AG8AYwBrAHAAaQBsAGUAKQBcACIALAAgADAALgAwADAANQAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBjAG8AbgBkAGEAcgB5AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAFAAYQBzAHMAaQB2AGUAIABXAGkAbgBkAHIAbwB3ACkAXAAiACwAIAAwAC4AMAAxACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAGMAbwBuAGQAYQByAHkAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AIAB0AG8AIABzAG8AaQBsAFwAIgAsACAAMAAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAcgB0AGkAYQByAHkAXAAiACwAIABcACIAVQBuAGMAbwB2AGUAcgBlAGQAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAKABFAGYAZgBsAHUAZQBuAHQAIABQAG8AbgBkACkAXAAiACwAIAAwACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBGAHIAYQBjAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADEALgA2ADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABiAHkAIABNAE0AUwAgACgARgByAGEAYwBHAEEAUwBNAG0AVAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARgByAGEAYwBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBlAGUAZABsAG8AdAAgAC0AIABGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAYgB5ACAATQBNAFMAIAAoAEYAcgBhAGMARwBBAFMATQBtAFQAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBGAHIAYQBjAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARgByAGEAYwBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADEALgA2ADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABiAHkAIABNAE0AUwAgACgARgByAGEAYwBHAEEAUwBNAG0AVAApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEYAcgBhAGMATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAATQBNAFMAIABuAGEAbQBlAHMAIAB0AGgAYQB0ACAAbQBhAHQAYwBoACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARgByAGEAYwBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgAFQAXAAiACwAIABcACIATQBNAFMAIABtAFwAIgAsACAAXAAiAEYAcgBhAGMARwBBAFMATQBtAFQAIAAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AXAAiACwAIABcACIATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAaQBtAGEAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAbABvAHQAIAAoAEYAZQBlAGQAcABhAGQAKQBcACIALAAgADAALgA2ACwAIABcACIARAByAHkAbABvAHQAIAAoAGYAZQBlAGQAIABwAGEAZAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGUAYwBvAG4AZABhAHIAeQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlACAAKABTAHQAbwBjAGsAcABpAGwAZQApAFwAIgAsACAAMAAuADIANQAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBjAG8AbgBkAGEAcgB5AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAFAAYQBzAHMAaQB2AGUAIABXAGkAbgBkAHIAbwB3ACkAXAAiACwAIAAwAC4ANAAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBjAG8AbgBkAGEAcgB5AFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAQQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgADAALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAHIAdABpAGEAcgB5AFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgARQBmAGYAbAB1AGUAbgB0ACAAcABvAG4AZAApAFwAIgAsACAAMAAuADMANQAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEYAZQBlAGQAbABvAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AMwAuADEAOgAgAEUAbgB0AGUAcgBpAGMAIABNAGUAdABoAGEAbgBlACAALQAgAEYAZQBlAGQAbABvAHQAIABCAGUAZQBmAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAzAC4AMQAuADEALgAxACAATQBlAHQAaABvAGQAIAAxACAALQAgAEUAbgB0AGUAcgBpAGMAIABCAGUAZQBmACAARgBlAGUAZABsAG8AdABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXABuAFQAbwB0AGEAbAAgAGEAbgBuAHUAYQBsACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAZQBuAHQAZQByAGkAYwAgAGYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACAAaQBuACAAZgBlAGUAZABsAG8AdAAgAGIAZQBlAGYAIABjAGEAdAB0AGwAZQBcAG4ARQBfAGUAbgB0AGUAcgBpAGMAXABuAHQAIABDAEgANABcAG4ARQBfAHsAZQBuAHQAZQByAGkAYwB9AD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBqACgARABfAGoAXABcAHQAaQBtAGUAcwAgAE0AXwBqAFwAXAB0AGkAbQBlAHMAIABOAF8AagApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBEAF8AagAgAD0AIABkAHUAcgBhAHQAaQBvAG4AIABvAGYAIABzAHQAYQB5ACAAbwBmACAAZQBhAGMAaAAgAGMAYQB0AHQAbABlACAAbABvAHQAIAAoAGQAYQB5AHMAKQBcAG4ATQBfAGoAIAA9ACAAZABhAGkAbAB5ACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIAAoAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5ACkAXABuAE4AXwBqACAAPQAgAG4AdQBtAGIAZQByAHMAIABvAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIABpAG4AIABlAGEAYwBoACAAYwBhAHQAdABsAGUAIABsAG8AdAAgACgAaABlAGEAZAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARABfAGoALAAgAE0AXwBqACwAIABOAF8AagAsAFwAbgAgACAAIAAgACgARABfAGoAIAAqACAATQBfAGoAIAAqACAATgBfAGoAKQAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABvAHQAYQBsACAAYQBuAG4AdQBhAGwAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABlAG4AdABlAHIAaQBjACAAZgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AIABpAG4AIABmAGUAZQBkAGwAbwB0ACAAYgBlAGUAZgAgAGMAYQB0AHQAbABlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AZQBuAHQAZQByAGkAYwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAEgANABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAzAC4AMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AGUAbgB0AGUAcgBpAGMAfQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AagAoAEQAXwBqAFwAXAB0AGkAbQBlAHMAIABNAF8AagBcAFwAdABpAG0AZQBzACAATgBfAGoAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAF8AagBcACIALAAgAFwAIgBkAHUAcgBhAHQAaQBvAG4AIABvAGYAIABzAHQAYQB5ACAAbwBmACAAZQBhAGMAaAAgAGMAYQB0AHQAbABlACAAbABvAHQAXAAiACwAIABcACIAZABhAHkAcwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AXwBqAFwAIgAsACAAXAAiAGQAYQBpAGwAeQAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuAFwAIgAsACAAXAAiAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAMwAuADEALgAxAC4AMQAsACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AXwBqAFwAIgAsACAAXAAiAG4AdQBtAGIAZQByAHMAIABvAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIABpAG4AIABlAGEAYwBoACAAYwBhAHQAdABsAGUAIABsAG8AdABcACIALAAgAFwAIgBoAGUAYQBkAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgBEAGEAaQBsAHkAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAZQBuAHQAZQByAGkAYwAgAG0AZQB0AGgAYQBuAGUAXABuAE0AXwBqAFwAbgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcAG4ATQBfAGoAPQAoADUALgAxADEAXABcAHQAaQBtAGUAcwAgAEkAXwBqAC0ANAAuADAAMABcAFwAdABpAG0AZQBzACAARQBFAF8AagArADIALgAyADYAXABcAHQAaQBtAGUAcwAgAE4ARABGAF8AagApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBJAF8AagAgAD0AIABkAHIAeQAgAG0AYQB0AHQAZQByACAAaQBuAHQAYQBrAGUAIAAoAGsAZwAgAEQATQAvAGgAZQBhAGQALwBkAGEAeQApAFwAbgBFAEUAXwBqACAAPQAgAGUAdABoAGUAcgAgAGUAeAB0AHIAYQBjAHQAIABhAHMAIABhACAAcABlAHIAYwBlAG4AdABhAGcAZQAgAG8AZgAgAEkAXwBqACAAKABwAGUAcgAgAGMAZQBuAHQAKQBcAG4ATgBEAEYAXwBqACAAPQAgAG4AZQB1AHQAcgBhAGwAIABkAGUAdABlAHIAZwBlAG4AdAAgAGYAaQBiAHIAZQAgAGEAcwAgAGEAIABwAGUAcgBjAGUAbgB0AGEAZwBlACAAbwBmACAASQBfAGoAIAAoAHAAZQByACAAYwBlAG4AdAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAASQBfAGoALAAgAEUARQBfAGoALAAgAE4ARABGAF8AagAsAFwAbgAgACAAIAAgACgANQAuADEAMQAgACoAIABJAF8AagAgAC0AIAA0AC4AMAAwACAAKgAgAEUARQBfAGoAIAArACAAMgAuADIANgAgACoAIABOAEQARgBfAGoAKQAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARABhAGkAbAB5ACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAGUAbgB0AGUAcgBpAGMAIABtAGUAdABoAGEAbgBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADMALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAbABtAGUAaQBkAGEAIABlAHQAIABhAGwALgAgACgAMgAwADIANQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAGoAPQAoADUALgAxADEAXABcAHQAaQBtAGUAcwAgAEkAXwBqAC0ANAAuADAAMABcAFwAdABpAG0AZQBzACAARQBFAF8AagArADIALgAyADYAXABcAHQAaQBtAGUAcwAgAE4ARABGAF8AagApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAXwBqAFwAIgAsACAAXAAiAGQAcgB5ACAAbQBhAHQAdABlAHIAIABpAG4AdABhAGsAZQBcACIALAAgAFwAIgBrAGcAIABEAE0ALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEUAXwBqAFwAIgAsACAAXAAiAGUAdABoAGUAcgAgAGUAeAB0AHIAYQBjAHQAIABhAHMAIABhACAAcABlAHIAYwBlAG4AdABhAGcAZQAgAG8AZgAgAEkAXwBqAFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARABGAF8AagBcACIALAAgAFwAIgBuAGUAdQB0AHIAYQBsACAAZABlAHQAZQByAGcAZQBuAHQAIABmAGkAYgByAGUAIABhAHMAIABhACAAcABlAHIAYwBlAG4AdABhAGcAZQAgAG8AZgAgAEkAXwBqAFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBWAGEAaQByAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEcAZQB0AE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBTAHQAYQBnAGUAMQBNAE0AUwBPAHAAdABpAG8AbgBzACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBTAHQAYQBnAGUAMgBNAE0AUwBPAHAAdABpAG8AbgBzACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBTAHQAYQBnAGUAMwBNAE0AUwBPAHAAdABpAG8AbgBzACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBMAGkAdgBlAHMAdABvAGMAawBDAGwAYQBzAHMAZQBzACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBuAGkAbQBhAGwAQwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAbgBpAG0AYQBsAEMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBuAGkAbQBhAGwAQwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBuAGkAbQBhAGwAQwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBuAGkAbQBhAGwAQwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAGkAZQB0AFAAcgBvAHAAZQByAHQAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAGkAZQB0AFAAcgBvAHAAZQByAHQAaQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARABpAGUAdABQAHIAbwBwAGUAcgB0AGkAZQBzAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBDAEYAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AQwBGAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBDAEYAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBDAEYAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBDAEYAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEYAcgBhAGMATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEYAcgBhAGMATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBGAHIAYQBjAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEYAcgBhAGMATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARgByAGEAYwBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAEQAYQB0AGEAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARgBlAGUAZABsAG8AdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBGAGUAZQBkAGwAbwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEYAZQBlAGQAbABvAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARgBlAGUAZABsAG8AdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARgBlAGUAZABsAG8AdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEYAZQBlAGQAbABvAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBGAGUAZQBkAGwAbwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBGAGUAZQBkAGwAbwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARgBlAGUAZABsAG8AdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBGAGUAZQBkAGwAbwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEYAZQBlAGQAbABvAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARgBlAGUAZABsAG8AdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARgBlAGUAZABsAG8AdABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADEAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEYAZQBlAGQAbABvAHQAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAxAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBGAGUAZQBkAGwAbwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBGAGUAZQBkAGwAbwB0AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMQBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -23201,7 +23307,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -23212,18 +23318,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>